--- a/GRÁFICO MACROFLUXO.xlsx
+++ b/GRÁFICO MACROFLUXO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Viana e Moura\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{001E3093-F7DE-4256-9B67-B94F0E3D0807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DEF5C4F-9B4A-4635-B6B8-B67E35026317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BD" sheetId="3" r:id="rId1"/>
@@ -1311,13 +1311,44 @@
     <xf numFmtId="14" fontId="7" fillId="16" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1341,45 +1372,14 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -6941,279 +6941,279 @@
       <c r="DH1" s="75"/>
     </row>
     <row r="2" spans="2:112" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="89"/>
-      <c r="C2" s="90"/>
-      <c r="D2" s="90"/>
+      <c r="B2" s="100"/>
+      <c r="C2" s="101"/>
+      <c r="D2" s="101"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="91" t="s">
+      <c r="F2" s="102" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="92"/>
-      <c r="H2" s="92"/>
-      <c r="I2" s="92"/>
-      <c r="J2" s="92"/>
-      <c r="K2" s="92"/>
-      <c r="L2" s="92"/>
-      <c r="M2" s="92"/>
-      <c r="N2" s="92"/>
-      <c r="O2" s="92"/>
-      <c r="P2" s="92"/>
-      <c r="Q2" s="92"/>
-      <c r="S2" s="93" t="s">
+      <c r="G2" s="103"/>
+      <c r="H2" s="103"/>
+      <c r="I2" s="103"/>
+      <c r="J2" s="103"/>
+      <c r="K2" s="103"/>
+      <c r="L2" s="103"/>
+      <c r="M2" s="103"/>
+      <c r="N2" s="103"/>
+      <c r="O2" s="103"/>
+      <c r="P2" s="103"/>
+      <c r="Q2" s="103"/>
+      <c r="S2" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="T2" s="93"/>
-      <c r="U2" s="93"/>
-      <c r="V2" s="93"/>
-      <c r="W2" s="93"/>
-      <c r="X2" s="93"/>
-      <c r="Y2" s="93"/>
-      <c r="Z2" s="93"/>
-      <c r="AA2" s="93"/>
-      <c r="AB2" s="93"/>
-      <c r="AC2" s="93"/>
-      <c r="AD2" s="93"/>
-      <c r="AE2" s="93"/>
-      <c r="AF2" s="93"/>
-      <c r="AG2" s="93"/>
+      <c r="T2" s="104"/>
+      <c r="U2" s="104"/>
+      <c r="V2" s="104"/>
+      <c r="W2" s="104"/>
+      <c r="X2" s="104"/>
+      <c r="Y2" s="104"/>
+      <c r="Z2" s="104"/>
+      <c r="AA2" s="104"/>
+      <c r="AB2" s="104"/>
+      <c r="AC2" s="104"/>
+      <c r="AD2" s="104"/>
+      <c r="AE2" s="104"/>
+      <c r="AF2" s="104"/>
+      <c r="AG2" s="104"/>
       <c r="AH2" s="2"/>
-      <c r="AI2" s="94" t="s">
+      <c r="AI2" s="105" t="s">
         <v>2</v>
       </c>
-      <c r="AJ2" s="94"/>
-      <c r="AK2" s="94"/>
-      <c r="AL2" s="94"/>
-      <c r="AM2" s="94"/>
-      <c r="AN2" s="94"/>
-      <c r="AO2" s="94"/>
-      <c r="AP2" s="94"/>
-      <c r="AQ2" s="94"/>
-      <c r="AR2" s="94"/>
-      <c r="AS2" s="94"/>
-      <c r="AT2" s="94"/>
-      <c r="AU2" s="94"/>
-      <c r="AV2" s="94"/>
-      <c r="AW2" s="94"/>
-      <c r="AX2" s="94"/>
+      <c r="AJ2" s="105"/>
+      <c r="AK2" s="105"/>
+      <c r="AL2" s="105"/>
+      <c r="AM2" s="105"/>
+      <c r="AN2" s="105"/>
+      <c r="AO2" s="105"/>
+      <c r="AP2" s="105"/>
+      <c r="AQ2" s="105"/>
+      <c r="AR2" s="105"/>
+      <c r="AS2" s="105"/>
+      <c r="AT2" s="105"/>
+      <c r="AU2" s="105"/>
+      <c r="AV2" s="105"/>
+      <c r="AW2" s="105"/>
+      <c r="AX2" s="105"/>
       <c r="AY2" s="2"/>
-      <c r="AZ2" s="95" t="s">
+      <c r="AZ2" s="106" t="s">
         <v>3</v>
       </c>
-      <c r="BA2" s="95"/>
-      <c r="BB2" s="95"/>
-      <c r="BC2" s="95"/>
-      <c r="BD2" s="95"/>
-      <c r="BE2" s="95"/>
-      <c r="BF2" s="95"/>
-      <c r="BG2" s="95"/>
-      <c r="BH2" s="95"/>
-      <c r="BI2" s="95"/>
-      <c r="BJ2" s="95"/>
-      <c r="BK2" s="95"/>
-      <c r="BL2" s="95"/>
-      <c r="BM2" s="95"/>
-      <c r="BN2" s="95"/>
-      <c r="BO2" s="104"/>
-      <c r="BP2" s="104"/>
-      <c r="BQ2" s="104"/>
-      <c r="BR2" s="104"/>
-      <c r="BS2" s="104"/>
-      <c r="BT2" s="104"/>
-      <c r="BU2" s="104"/>
-      <c r="BV2" s="104"/>
-      <c r="BX2" s="96" t="s">
+      <c r="BA2" s="106"/>
+      <c r="BB2" s="106"/>
+      <c r="BC2" s="106"/>
+      <c r="BD2" s="106"/>
+      <c r="BE2" s="106"/>
+      <c r="BF2" s="106"/>
+      <c r="BG2" s="106"/>
+      <c r="BH2" s="106"/>
+      <c r="BI2" s="106"/>
+      <c r="BJ2" s="106"/>
+      <c r="BK2" s="106"/>
+      <c r="BL2" s="106"/>
+      <c r="BM2" s="106"/>
+      <c r="BN2" s="106"/>
+      <c r="BO2" s="99"/>
+      <c r="BP2" s="99"/>
+      <c r="BQ2" s="99"/>
+      <c r="BR2" s="99"/>
+      <c r="BS2" s="99"/>
+      <c r="BT2" s="99"/>
+      <c r="BU2" s="99"/>
+      <c r="BV2" s="99"/>
+      <c r="BX2" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="BY2" s="96"/>
-      <c r="BZ2" s="96"/>
+      <c r="BY2" s="91"/>
+      <c r="BZ2" s="91"/>
       <c r="CA2" s="3"/>
       <c r="CB2" s="4"/>
       <c r="CC2" s="4"/>
       <c r="CD2" s="4"/>
       <c r="CE2" s="4"/>
-      <c r="CF2" s="97" t="s">
+      <c r="CF2" s="92" t="s">
         <v>5</v>
       </c>
-      <c r="CG2" s="97"/>
-      <c r="CH2" s="97"/>
-      <c r="CI2" s="97"/>
-      <c r="CJ2" s="97"/>
-      <c r="CK2" s="97"/>
-      <c r="CL2" s="97"/>
-      <c r="CM2" s="97"/>
-      <c r="CN2" s="98"/>
+      <c r="CG2" s="92"/>
+      <c r="CH2" s="92"/>
+      <c r="CI2" s="92"/>
+      <c r="CJ2" s="92"/>
+      <c r="CK2" s="92"/>
+      <c r="CL2" s="92"/>
+      <c r="CM2" s="92"/>
+      <c r="CN2" s="93"/>
       <c r="CO2" s="5">
         <v>45839</v>
       </c>
-      <c r="CP2" s="86" t="s">
+      <c r="CP2" s="107" t="s">
         <v>160</v>
       </c>
-      <c r="CQ2" s="87"/>
-      <c r="CR2" s="87"/>
-      <c r="CS2" s="87"/>
-      <c r="CT2" s="87"/>
-      <c r="CU2" s="87"/>
-      <c r="CV2" s="87"/>
-      <c r="CW2" s="87"/>
-      <c r="CX2" s="87"/>
-      <c r="CY2" s="87"/>
-      <c r="CZ2" s="87"/>
-      <c r="DA2" s="87"/>
-      <c r="DB2" s="87"/>
-      <c r="DC2" s="87"/>
-      <c r="DD2" s="87"/>
-      <c r="DE2" s="87"/>
-      <c r="DF2" s="87"/>
-      <c r="DG2" s="87"/>
-      <c r="DH2" s="87"/>
+      <c r="CQ2" s="108"/>
+      <c r="CR2" s="108"/>
+      <c r="CS2" s="108"/>
+      <c r="CT2" s="108"/>
+      <c r="CU2" s="108"/>
+      <c r="CV2" s="108"/>
+      <c r="CW2" s="108"/>
+      <c r="CX2" s="108"/>
+      <c r="CY2" s="108"/>
+      <c r="CZ2" s="108"/>
+      <c r="DA2" s="108"/>
+      <c r="DB2" s="108"/>
+      <c r="DC2" s="108"/>
+      <c r="DD2" s="108"/>
+      <c r="DE2" s="108"/>
+      <c r="DF2" s="108"/>
+      <c r="DG2" s="108"/>
+      <c r="DH2" s="108"/>
     </row>
     <row r="3" spans="2:112" x14ac:dyDescent="0.3">
       <c r="B3" s="6"/>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
-      <c r="F3" s="99" t="s">
+      <c r="F3" s="94" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="100"/>
-      <c r="H3" s="100"/>
+      <c r="G3" s="95"/>
+      <c r="H3" s="95"/>
       <c r="I3" s="8"/>
-      <c r="J3" s="100" t="s">
+      <c r="J3" s="95" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="100"/>
-      <c r="L3" s="100"/>
+      <c r="K3" s="95"/>
+      <c r="L3" s="95"/>
       <c r="M3" s="8"/>
-      <c r="N3" s="101" t="s">
+      <c r="N3" s="96" t="s">
         <v>8</v>
       </c>
-      <c r="O3" s="101"/>
-      <c r="P3" s="101"/>
-      <c r="Q3" s="102"/>
-      <c r="S3" s="106" t="s">
+      <c r="O3" s="96"/>
+      <c r="P3" s="96"/>
+      <c r="Q3" s="97"/>
+      <c r="S3" s="98" t="s">
         <v>9</v>
       </c>
-      <c r="T3" s="106"/>
-      <c r="U3" s="106"/>
-      <c r="W3" s="106" t="s">
+      <c r="T3" s="98"/>
+      <c r="U3" s="98"/>
+      <c r="W3" s="98" t="s">
         <v>10</v>
       </c>
-      <c r="X3" s="106"/>
-      <c r="Y3" s="106"/>
-      <c r="AA3" s="106" t="s">
+      <c r="X3" s="98"/>
+      <c r="Y3" s="98"/>
+      <c r="AA3" s="98" t="s">
         <v>11</v>
       </c>
-      <c r="AB3" s="106"/>
-      <c r="AC3" s="106"/>
-      <c r="AE3" s="103" t="s">
+      <c r="AB3" s="98"/>
+      <c r="AC3" s="98"/>
+      <c r="AE3" s="89" t="s">
         <v>12</v>
       </c>
-      <c r="AF3" s="103"/>
-      <c r="AG3" s="103"/>
-      <c r="AI3" s="106" t="s">
+      <c r="AF3" s="89"/>
+      <c r="AG3" s="89"/>
+      <c r="AI3" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="AJ3" s="106"/>
-      <c r="AK3" s="106"/>
-      <c r="AM3" s="106" t="s">
+      <c r="AJ3" s="98"/>
+      <c r="AK3" s="98"/>
+      <c r="AM3" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="AN3" s="106"/>
-      <c r="AO3" s="106"/>
-      <c r="AQ3" s="103" t="s">
+      <c r="AN3" s="98"/>
+      <c r="AO3" s="98"/>
+      <c r="AQ3" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="AR3" s="103"/>
-      <c r="AS3" s="103"/>
-      <c r="AT3" s="103"/>
-      <c r="AV3" s="103" t="s">
+      <c r="AR3" s="89"/>
+      <c r="AS3" s="89"/>
+      <c r="AT3" s="89"/>
+      <c r="AV3" s="89" t="s">
         <v>16</v>
       </c>
-      <c r="AW3" s="103"/>
-      <c r="AX3" s="103"/>
-      <c r="AZ3" s="103" t="s">
+      <c r="AW3" s="89"/>
+      <c r="AX3" s="89"/>
+      <c r="AZ3" s="89" t="s">
         <v>17</v>
       </c>
-      <c r="BA3" s="103"/>
-      <c r="BB3" s="103"/>
-      <c r="BD3" s="103" t="s">
+      <c r="BA3" s="89"/>
+      <c r="BB3" s="89"/>
+      <c r="BD3" s="89" t="s">
         <v>18</v>
       </c>
-      <c r="BE3" s="103"/>
-      <c r="BF3" s="103"/>
-      <c r="BH3" s="103" t="s">
+      <c r="BE3" s="89"/>
+      <c r="BF3" s="89"/>
+      <c r="BH3" s="89" t="s">
         <v>19</v>
       </c>
-      <c r="BI3" s="103"/>
-      <c r="BJ3" s="103"/>
-      <c r="BL3" s="103" t="s">
+      <c r="BI3" s="89"/>
+      <c r="BJ3" s="89"/>
+      <c r="BL3" s="89" t="s">
         <v>20</v>
       </c>
-      <c r="BM3" s="103"/>
-      <c r="BN3" s="103"/>
-      <c r="BP3" s="103" t="s">
+      <c r="BM3" s="89"/>
+      <c r="BN3" s="89"/>
+      <c r="BP3" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="BQ3" s="103"/>
-      <c r="BR3" s="103"/>
-      <c r="BT3" s="103" t="s">
+      <c r="BQ3" s="89"/>
+      <c r="BR3" s="89"/>
+      <c r="BT3" s="89" t="s">
         <v>22</v>
       </c>
-      <c r="BU3" s="103"/>
-      <c r="BV3" s="103"/>
-      <c r="BX3" s="103" t="s">
+      <c r="BU3" s="89"/>
+      <c r="BV3" s="89"/>
+      <c r="BX3" s="89" t="s">
         <v>23</v>
       </c>
-      <c r="BY3" s="103"/>
-      <c r="BZ3" s="103"/>
-      <c r="CB3" s="103" t="s">
+      <c r="BY3" s="89"/>
+      <c r="BZ3" s="89"/>
+      <c r="CB3" s="89" t="s">
         <v>24</v>
       </c>
-      <c r="CC3" s="103"/>
-      <c r="CD3" s="103"/>
-      <c r="CF3" s="103" t="s">
+      <c r="CC3" s="89"/>
+      <c r="CD3" s="89"/>
+      <c r="CF3" s="89" t="s">
         <v>25</v>
       </c>
-      <c r="CG3" s="103"/>
-      <c r="CH3" s="103"/>
-      <c r="CJ3" s="88" t="s">
+      <c r="CG3" s="89"/>
+      <c r="CH3" s="89"/>
+      <c r="CJ3" s="90" t="s">
         <v>26</v>
       </c>
-      <c r="CK3" s="88"/>
-      <c r="CL3" s="88"/>
+      <c r="CK3" s="90"/>
+      <c r="CL3" s="90"/>
       <c r="CN3" s="9" t="s">
         <v>5</v>
       </c>
       <c r="CO3" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="CP3" s="88" t="s">
+      <c r="CP3" s="90" t="s">
         <v>148</v>
       </c>
-      <c r="CQ3" s="88"/>
-      <c r="CR3" s="88"/>
+      <c r="CQ3" s="90"/>
+      <c r="CR3" s="90"/>
       <c r="CS3" s="72"/>
-      <c r="CT3" s="88" t="s">
+      <c r="CT3" s="90" t="s">
         <v>147</v>
       </c>
-      <c r="CU3" s="88"/>
-      <c r="CV3" s="88"/>
+      <c r="CU3" s="90"/>
+      <c r="CV3" s="90"/>
       <c r="CW3" s="72"/>
-      <c r="CX3" s="88" t="s">
+      <c r="CX3" s="90" t="s">
         <v>146</v>
       </c>
-      <c r="CY3" s="88"/>
-      <c r="CZ3" s="88"/>
+      <c r="CY3" s="90"/>
+      <c r="CZ3" s="90"/>
       <c r="DA3" s="72"/>
-      <c r="DB3" s="88" t="s">
+      <c r="DB3" s="90" t="s">
         <v>149</v>
       </c>
-      <c r="DC3" s="88"/>
-      <c r="DD3" s="88"/>
-      <c r="DF3" s="88" t="s">
+      <c r="DC3" s="90"/>
+      <c r="DD3" s="90"/>
+      <c r="DF3" s="90" t="s">
         <v>145</v>
       </c>
-      <c r="DG3" s="88"/>
-      <c r="DH3" s="88"/>
+      <c r="DG3" s="90"/>
+      <c r="DH3" s="90"/>
     </row>
     <row r="4" spans="2:112" x14ac:dyDescent="0.3">
       <c r="B4" s="10"/>
@@ -7622,224 +7622,224 @@
       <c r="D7" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="107"/>
-      <c r="F7" s="108" t="s">
+      <c r="E7" s="86"/>
+      <c r="F7" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="108" t="s">
+      <c r="G7" s="87" t="s">
         <v>35</v>
       </c>
-      <c r="H7" s="108"/>
-      <c r="I7" s="107"/>
-      <c r="J7" s="108" t="s">
+      <c r="H7" s="87"/>
+      <c r="I7" s="86"/>
+      <c r="J7" s="87" t="s">
         <v>36</v>
       </c>
-      <c r="K7" s="108" t="s">
+      <c r="K7" s="87" t="s">
         <v>122</v>
       </c>
-      <c r="L7" s="108"/>
-      <c r="M7" s="107"/>
-      <c r="N7" s="108" t="s">
+      <c r="L7" s="87"/>
+      <c r="M7" s="86"/>
+      <c r="N7" s="87" t="s">
         <v>37</v>
       </c>
-      <c r="O7" s="108" t="s">
+      <c r="O7" s="87" t="s">
         <v>38</v>
       </c>
-      <c r="P7" s="108"/>
-      <c r="Q7" s="108" t="s">
+      <c r="P7" s="87"/>
+      <c r="Q7" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="R7" s="107"/>
-      <c r="S7" s="108" t="s">
+      <c r="R7" s="86"/>
+      <c r="S7" s="87" t="s">
         <v>40</v>
       </c>
-      <c r="T7" s="108" t="s">
+      <c r="T7" s="87" t="s">
         <v>41</v>
       </c>
-      <c r="U7" s="108"/>
-      <c r="V7" s="107"/>
-      <c r="W7" s="108" t="s">
+      <c r="U7" s="87"/>
+      <c r="V7" s="86"/>
+      <c r="W7" s="87" t="s">
         <v>42</v>
       </c>
-      <c r="X7" s="108" t="s">
+      <c r="X7" s="87" t="s">
         <v>43</v>
       </c>
-      <c r="Y7" s="108"/>
-      <c r="Z7" s="107"/>
-      <c r="AA7" s="108" t="s">
+      <c r="Y7" s="87"/>
+      <c r="Z7" s="86"/>
+      <c r="AA7" s="87" t="s">
         <v>44</v>
       </c>
-      <c r="AB7" s="108" t="s">
+      <c r="AB7" s="87" t="s">
         <v>45</v>
       </c>
-      <c r="AC7" s="108"/>
-      <c r="AD7" s="107"/>
-      <c r="AE7" s="108" t="s">
+      <c r="AC7" s="87"/>
+      <c r="AD7" s="86"/>
+      <c r="AE7" s="87" t="s">
         <v>46</v>
       </c>
-      <c r="AF7" s="108" t="s">
+      <c r="AF7" s="87" t="s">
         <v>47</v>
       </c>
-      <c r="AG7" s="108"/>
-      <c r="AH7" s="107"/>
-      <c r="AI7" s="108" t="s">
+      <c r="AG7" s="87"/>
+      <c r="AH7" s="86"/>
+      <c r="AI7" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="AJ7" s="108" t="s">
+      <c r="AJ7" s="87" t="s">
         <v>49</v>
       </c>
-      <c r="AK7" s="108"/>
-      <c r="AL7" s="107"/>
-      <c r="AM7" s="108" t="s">
+      <c r="AK7" s="87"/>
+      <c r="AL7" s="86"/>
+      <c r="AM7" s="87" t="s">
         <v>50</v>
       </c>
-      <c r="AN7" s="108" t="s">
+      <c r="AN7" s="87" t="s">
         <v>51</v>
       </c>
-      <c r="AO7" s="108"/>
-      <c r="AP7" s="107"/>
-      <c r="AQ7" s="108" t="s">
+      <c r="AO7" s="87"/>
+      <c r="AP7" s="86"/>
+      <c r="AQ7" s="87" t="s">
         <v>52</v>
       </c>
-      <c r="AR7" s="108" t="s">
+      <c r="AR7" s="87" t="s">
         <v>53</v>
       </c>
-      <c r="AS7" s="108"/>
-      <c r="AT7" s="108"/>
-      <c r="AU7" s="107"/>
-      <c r="AV7" s="108" t="s">
+      <c r="AS7" s="87"/>
+      <c r="AT7" s="87"/>
+      <c r="AU7" s="86"/>
+      <c r="AV7" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="AW7" s="108" t="s">
+      <c r="AW7" s="87" t="s">
         <v>55</v>
       </c>
-      <c r="AX7" s="108"/>
-      <c r="AY7" s="107"/>
-      <c r="AZ7" s="108" t="s">
+      <c r="AX7" s="87"/>
+      <c r="AY7" s="86"/>
+      <c r="AZ7" s="87" t="s">
         <v>56</v>
       </c>
-      <c r="BA7" s="108" t="s">
+      <c r="BA7" s="87" t="s">
         <v>57</v>
       </c>
-      <c r="BB7" s="108"/>
-      <c r="BC7" s="107"/>
-      <c r="BD7" s="108" t="s">
+      <c r="BB7" s="87"/>
+      <c r="BC7" s="86"/>
+      <c r="BD7" s="87" t="s">
         <v>58</v>
       </c>
-      <c r="BE7" s="108" t="s">
+      <c r="BE7" s="87" t="s">
         <v>59</v>
       </c>
-      <c r="BF7" s="108"/>
-      <c r="BG7" s="107"/>
-      <c r="BH7" s="108" t="s">
+      <c r="BF7" s="87"/>
+      <c r="BG7" s="86"/>
+      <c r="BH7" s="87" t="s">
         <v>60</v>
       </c>
-      <c r="BI7" s="108" t="s">
+      <c r="BI7" s="87" t="s">
         <v>61</v>
       </c>
-      <c r="BJ7" s="108"/>
-      <c r="BK7" s="107"/>
-      <c r="BL7" s="108" t="s">
+      <c r="BJ7" s="87"/>
+      <c r="BK7" s="86"/>
+      <c r="BL7" s="87" t="s">
         <v>62</v>
       </c>
-      <c r="BM7" s="108" t="s">
+      <c r="BM7" s="87" t="s">
         <v>63</v>
       </c>
-      <c r="BN7" s="108"/>
-      <c r="BO7" s="107"/>
-      <c r="BP7" s="108" t="s">
+      <c r="BN7" s="87"/>
+      <c r="BO7" s="86"/>
+      <c r="BP7" s="87" t="s">
         <v>64</v>
       </c>
-      <c r="BQ7" s="108" t="s">
+      <c r="BQ7" s="87" t="s">
         <v>65</v>
       </c>
-      <c r="BR7" s="108"/>
-      <c r="BS7" s="107"/>
-      <c r="BT7" s="108" t="s">
+      <c r="BR7" s="87"/>
+      <c r="BS7" s="86"/>
+      <c r="BT7" s="87" t="s">
         <v>66</v>
       </c>
-      <c r="BU7" s="108" t="s">
+      <c r="BU7" s="87" t="s">
         <v>67</v>
       </c>
-      <c r="BV7" s="108"/>
-      <c r="BW7" s="107"/>
-      <c r="BX7" s="108" t="s">
+      <c r="BV7" s="87"/>
+      <c r="BW7" s="86"/>
+      <c r="BX7" s="87" t="s">
         <v>68</v>
       </c>
-      <c r="BY7" s="108" t="s">
+      <c r="BY7" s="87" t="s">
         <v>69</v>
       </c>
       <c r="BZ7" s="13"/>
-      <c r="CA7" s="107"/>
-      <c r="CB7" s="108" t="s">
+      <c r="CA7" s="86"/>
+      <c r="CB7" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="CC7" s="108" t="s">
+      <c r="CC7" s="87" t="s">
         <v>71</v>
       </c>
       <c r="CD7" s="13"/>
-      <c r="CE7" s="107"/>
-      <c r="CF7" s="108" t="s">
+      <c r="CE7" s="86"/>
+      <c r="CF7" s="87" t="s">
         <v>72</v>
       </c>
-      <c r="CG7" s="108" t="s">
+      <c r="CG7" s="87" t="s">
         <v>73</v>
       </c>
       <c r="CH7" s="13"/>
-      <c r="CI7" s="107"/>
-      <c r="CJ7" s="108" t="s">
+      <c r="CI7" s="86"/>
+      <c r="CJ7" s="87" t="s">
         <v>74</v>
       </c>
-      <c r="CK7" s="108" t="s">
+      <c r="CK7" s="87" t="s">
         <v>75</v>
       </c>
-      <c r="CL7" s="108"/>
-      <c r="CM7" s="107"/>
-      <c r="CN7" s="108" t="s">
+      <c r="CL7" s="87"/>
+      <c r="CM7" s="86"/>
+      <c r="CN7" s="87" t="s">
         <v>76</v>
       </c>
-      <c r="CO7" s="108" t="s">
+      <c r="CO7" s="87" t="s">
         <v>77</v>
       </c>
-      <c r="CP7" s="108" t="s">
+      <c r="CP7" s="87" t="s">
         <v>152</v>
       </c>
-      <c r="CQ7" s="108" t="s">
+      <c r="CQ7" s="87" t="s">
         <v>153</v>
       </c>
-      <c r="CR7" s="108"/>
-      <c r="CS7" s="109"/>
-      <c r="CT7" s="108" t="s">
+      <c r="CR7" s="87"/>
+      <c r="CS7" s="88"/>
+      <c r="CT7" s="87" t="s">
         <v>150</v>
       </c>
-      <c r="CU7" s="108" t="s">
+      <c r="CU7" s="87" t="s">
         <v>151</v>
       </c>
-      <c r="CV7" s="108"/>
-      <c r="CW7" s="109"/>
-      <c r="CX7" s="108" t="s">
+      <c r="CV7" s="87"/>
+      <c r="CW7" s="88"/>
+      <c r="CX7" s="87" t="s">
         <v>154</v>
       </c>
-      <c r="CY7" s="108" t="s">
+      <c r="CY7" s="87" t="s">
         <v>155</v>
       </c>
-      <c r="CZ7" s="108"/>
-      <c r="DA7" s="109"/>
-      <c r="DB7" s="108" t="s">
+      <c r="CZ7" s="87"/>
+      <c r="DA7" s="88"/>
+      <c r="DB7" s="87" t="s">
         <v>156</v>
       </c>
-      <c r="DC7" s="108" t="s">
+      <c r="DC7" s="87" t="s">
         <v>157</v>
       </c>
-      <c r="DD7" s="108"/>
-      <c r="DE7" s="109"/>
-      <c r="DF7" s="108" t="s">
+      <c r="DD7" s="87"/>
+      <c r="DE7" s="88"/>
+      <c r="DF7" s="87" t="s">
         <v>158</v>
       </c>
-      <c r="DG7" s="108" t="s">
+      <c r="DG7" s="87" t="s">
         <v>159</v>
       </c>
-      <c r="DH7" s="108"/>
+      <c r="DH7" s="87"/>
     </row>
     <row r="8" spans="2:112" x14ac:dyDescent="0.3">
       <c r="B8" s="14" t="s">
@@ -8001,9 +8001,11 @@
         <v>155</v>
       </c>
       <c r="BH8" s="18">
+        <f>WORKDAY(BI8,-BJ8)</f>
         <v>46029</v>
       </c>
       <c r="BI8" s="18">
+        <f>WORKDAY(BL8,-1)</f>
         <v>46155</v>
       </c>
       <c r="BJ8" s="16">
@@ -8032,9 +8034,11 @@
         <v>75</v>
       </c>
       <c r="BT8" s="18">
+        <f>EDATE(BU8,-BV8)</f>
         <v>46217</v>
       </c>
       <c r="BU8" s="18">
+        <f>WORKDAY(BX8,-1)</f>
         <v>46309</v>
       </c>
       <c r="BV8" s="16">
@@ -8310,47 +8314,51 @@
         <v>155</v>
       </c>
       <c r="BH9" s="31">
+        <f t="shared" ref="BH9:BH30" si="27">WORKDAY(BI9,-BJ9)</f>
         <v>45541</v>
       </c>
       <c r="BI9" s="31">
+        <f t="shared" ref="BI9:BI30" si="28">WORKDAY(BL9,-1)</f>
         <v>45667</v>
       </c>
       <c r="BJ9" s="29">
         <v>90</v>
       </c>
       <c r="BL9" s="31">
-        <f t="shared" ref="BL9:BL30" si="27">EDATE(BM9,-BN9)</f>
+        <f t="shared" ref="BL9:BL30" si="29">EDATE(BM9,-BN9)</f>
         <v>45669</v>
       </c>
       <c r="BM9" s="31">
-        <f t="shared" ref="BM9:BM30" si="28">BX9-1</f>
+        <f t="shared" ref="BM9:BM30" si="30">BX9-1</f>
         <v>45820</v>
       </c>
       <c r="BN9" s="29">
         <v>5</v>
       </c>
       <c r="BP9" s="31">
-        <f t="shared" ref="BP9:BP30" si="29">WORKDAY(BQ9,-BR9)</f>
+        <f t="shared" ref="BP9:BP30" si="31">WORKDAY(BQ9,-BR9)</f>
         <v>45622</v>
       </c>
       <c r="BQ9" s="31">
-        <f t="shared" ref="BQ9:BQ30" si="30">WORKDAY(BT9,-1)</f>
+        <f t="shared" ref="BQ9:BQ30" si="32">WORKDAY(BT9,-1)</f>
         <v>45727</v>
       </c>
       <c r="BR9" s="29">
         <v>75</v>
       </c>
       <c r="BT9" s="31">
+        <f t="shared" ref="BT9:BT30" si="33">EDATE(BU9,-BV9)</f>
         <v>45728</v>
       </c>
       <c r="BU9" s="31">
+        <f t="shared" ref="BU9:BU30" si="34">WORKDAY(BX9,-1)</f>
         <v>45820</v>
       </c>
       <c r="BV9" s="29">
         <v>3</v>
       </c>
       <c r="BX9" s="31">
-        <f t="shared" ref="BX9:BX30" si="31">EDATE(BY9,-BZ9)</f>
+        <f t="shared" ref="BX9:BX30" si="35">EDATE(BY9,-BZ9)</f>
         <v>45821</v>
       </c>
       <c r="BY9" s="31">
@@ -8361,33 +8369,33 @@
         <v>0</v>
       </c>
       <c r="CB9" s="34">
-        <f t="shared" ref="CB9:CB30" si="32">WORKDAY(CC9,-CD9)</f>
+        <f t="shared" ref="CB9:CB30" si="36">WORKDAY(CC9,-CD9)</f>
         <v>45159</v>
       </c>
       <c r="CC9" s="34">
-        <f t="shared" ref="CC9:CC30" si="33">WORKDAY(CF9,-1)</f>
+        <f t="shared" ref="CC9:CC30" si="37">WORKDAY(CF9,-1)</f>
         <v>45271</v>
       </c>
       <c r="CD9" s="29">
         <v>80</v>
       </c>
       <c r="CF9" s="34">
-        <f t="shared" ref="CF9:CF30" si="34">EDATE(CG9,-CH9)</f>
+        <f t="shared" ref="CF9:CF30" si="38">EDATE(CG9,-CH9)</f>
         <v>45272</v>
       </c>
       <c r="CG9" s="34">
-        <f t="shared" ref="CG9:CG30" si="35">WORKDAY(CJ9,-1)</f>
+        <f t="shared" ref="CG9:CG30" si="39">WORKDAY(CJ9,-1)</f>
         <v>45820</v>
       </c>
       <c r="CH9" s="29">
         <v>18</v>
       </c>
       <c r="CJ9" s="34">
-        <f t="shared" ref="CJ9:CJ30" si="36">EDATE(CK9,-CL9)</f>
+        <f t="shared" ref="CJ9:CJ30" si="40">EDATE(CK9,-CL9)</f>
         <v>45821</v>
       </c>
       <c r="CK9" s="18">
-        <f t="shared" ref="CK9:CK30" si="37">WORKDAY(CN9,-1)</f>
+        <f t="shared" ref="CK9:CK30" si="41">WORKDAY(CN9,-1)</f>
         <v>45821</v>
       </c>
       <c r="CL9" s="29">
@@ -8400,11 +8408,11 @@
         <v>45839</v>
       </c>
       <c r="CP9" s="79">
-        <f t="shared" ref="CP9:CP30" si="38">EDATE(CT9,-CR9)</f>
+        <f t="shared" ref="CP9:CP30" si="42">EDATE(CT9,-CR9)</f>
         <v>45658</v>
       </c>
       <c r="CQ9" s="34">
-        <f t="shared" ref="CQ9:CQ30" si="39">EDATE(CP9,CR9)</f>
+        <f t="shared" ref="CQ9:CQ30" si="43">EDATE(CP9,CR9)</f>
         <v>45717</v>
       </c>
       <c r="CR9" s="80">
@@ -8412,11 +8420,11 @@
       </c>
       <c r="CS9" s="73"/>
       <c r="CT9" s="79">
-        <f t="shared" ref="CT9:CT30" si="40">EDATE(CX9,-CV9)</f>
+        <f t="shared" ref="CT9:CT30" si="44">EDATE(CX9,-CV9)</f>
         <v>45717</v>
       </c>
       <c r="CU9" s="34">
-        <f t="shared" ref="CU9:CU30" si="41">EDATE(CT9,CV9)</f>
+        <f t="shared" ref="CU9:CU30" si="45">EDATE(CT9,CV9)</f>
         <v>45778</v>
       </c>
       <c r="CV9" s="80">
@@ -8424,11 +8432,11 @@
       </c>
       <c r="CW9" s="73"/>
       <c r="CX9" s="79">
-        <f t="shared" ref="CX9:CX30" si="42">EDATE(DB9,-CZ9)</f>
+        <f t="shared" ref="CX9:CX30" si="46">EDATE(DB9,-CZ9)</f>
         <v>45778</v>
       </c>
       <c r="CY9" s="34">
-        <f t="shared" ref="CY9:CY30" si="43">EDATE(CX9,CZ9)</f>
+        <f t="shared" ref="CY9:CY30" si="47">EDATE(CX9,CZ9)</f>
         <v>45839</v>
       </c>
       <c r="CZ9" s="80">
@@ -8436,11 +8444,11 @@
       </c>
       <c r="DA9" s="73"/>
       <c r="DB9" s="79">
-        <f t="shared" ref="DB9:DB30" si="44">EDATE(DF9,-DD9)</f>
+        <f t="shared" ref="DB9:DB30" si="48">EDATE(DF9,-DD9)</f>
         <v>45839</v>
       </c>
       <c r="DC9" s="34">
-        <f t="shared" ref="DC9:DC30" si="45">EDATE(DB9,DD9)</f>
+        <f t="shared" ref="DC9:DC30" si="49">EDATE(DB9,DD9)</f>
         <v>45901</v>
       </c>
       <c r="DD9" s="80">
@@ -8448,11 +8456,11 @@
       </c>
       <c r="DE9" s="74"/>
       <c r="DF9" s="79">
-        <f t="shared" ref="DF9:DF30" si="46">EDATE(CO9,2)</f>
+        <f t="shared" ref="DF9:DF30" si="50">EDATE(CO9,2)</f>
         <v>45901</v>
       </c>
       <c r="DG9" s="34">
-        <f t="shared" ref="DG9:DG30" si="47">EDATE(DF9,DH9)</f>
+        <f t="shared" ref="DG9:DG30" si="51">EDATE(DF9,DH9)</f>
         <v>46113</v>
       </c>
       <c r="DH9" s="80">
@@ -8619,47 +8627,51 @@
         <v>155</v>
       </c>
       <c r="BH10" s="18">
+        <f t="shared" si="27"/>
         <v>45756</v>
       </c>
       <c r="BI10" s="18">
+        <f t="shared" si="28"/>
         <v>45882</v>
       </c>
       <c r="BJ10" s="16">
         <v>90</v>
       </c>
       <c r="BL10" s="18">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>45883</v>
       </c>
       <c r="BM10" s="18">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>46036</v>
       </c>
       <c r="BN10" s="16">
         <v>5</v>
       </c>
       <c r="BP10" s="18">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>45838</v>
       </c>
       <c r="BQ10" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>45943</v>
       </c>
       <c r="BR10" s="16">
         <v>75</v>
       </c>
       <c r="BT10" s="18">
+        <f t="shared" si="33"/>
         <v>45944</v>
       </c>
       <c r="BU10" s="18">
+        <f t="shared" si="34"/>
         <v>46036</v>
       </c>
       <c r="BV10" s="16">
         <v>3</v>
       </c>
       <c r="BX10" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>46037</v>
       </c>
       <c r="BY10" s="18">
@@ -8670,33 +8682,33 @@
         <v>0</v>
       </c>
       <c r="CB10" s="22">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>45373</v>
       </c>
       <c r="CC10" s="22">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>45485</v>
       </c>
       <c r="CD10" s="16">
         <v>80</v>
       </c>
       <c r="CF10" s="22">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>45487</v>
       </c>
       <c r="CG10" s="22">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>46036</v>
       </c>
       <c r="CH10" s="16">
         <v>18</v>
       </c>
       <c r="CJ10" s="22">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>46037</v>
       </c>
       <c r="CK10" s="18">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>46037</v>
       </c>
       <c r="CL10" s="16">
@@ -8709,11 +8721,11 @@
         <v>46054</v>
       </c>
       <c r="CP10" s="77">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>45870</v>
       </c>
       <c r="CQ10" s="22">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>45931</v>
       </c>
       <c r="CR10" s="78">
@@ -8721,11 +8733,11 @@
       </c>
       <c r="CS10" s="73"/>
       <c r="CT10" s="77">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>45931</v>
       </c>
       <c r="CU10" s="22">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>45992</v>
       </c>
       <c r="CV10" s="78">
@@ -8733,11 +8745,11 @@
       </c>
       <c r="CW10" s="73"/>
       <c r="CX10" s="77">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>45992</v>
       </c>
       <c r="CY10" s="22">
-        <f t="shared" si="43"/>
+        <f t="shared" si="47"/>
         <v>46054</v>
       </c>
       <c r="CZ10" s="78">
@@ -8745,11 +8757,11 @@
       </c>
       <c r="DA10" s="73"/>
       <c r="DB10" s="77">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>46054</v>
       </c>
       <c r="DC10" s="22">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>46113</v>
       </c>
       <c r="DD10" s="78">
@@ -8757,11 +8769,11 @@
       </c>
       <c r="DE10" s="74"/>
       <c r="DF10" s="77">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>46113</v>
       </c>
       <c r="DG10" s="22">
-        <f t="shared" si="47"/>
+        <f t="shared" si="51"/>
         <v>46327</v>
       </c>
       <c r="DH10" s="78">
@@ -8928,47 +8940,51 @@
         <v>155</v>
       </c>
       <c r="BH11" s="31">
+        <f t="shared" si="27"/>
         <v>46030</v>
       </c>
       <c r="BI11" s="31">
+        <f t="shared" si="28"/>
         <v>46156</v>
       </c>
       <c r="BJ11" s="29">
         <v>90</v>
       </c>
       <c r="BL11" s="31">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>46157</v>
       </c>
       <c r="BM11" s="31">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>46310</v>
       </c>
       <c r="BN11" s="29">
         <v>5</v>
       </c>
       <c r="BP11" s="31">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>46112</v>
       </c>
       <c r="BQ11" s="31">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>46217</v>
       </c>
       <c r="BR11" s="29">
         <v>75</v>
       </c>
       <c r="BT11" s="31">
+        <f t="shared" si="33"/>
         <v>46218</v>
       </c>
       <c r="BU11" s="31">
+        <f t="shared" si="34"/>
         <v>46310</v>
       </c>
       <c r="BV11" s="29">
         <v>3</v>
       </c>
       <c r="BX11" s="31">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>46311</v>
       </c>
       <c r="BY11" s="31">
@@ -8979,33 +8995,33 @@
         <v>0</v>
       </c>
       <c r="CB11" s="34">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>45649</v>
       </c>
       <c r="CC11" s="34">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>45761</v>
       </c>
       <c r="CD11" s="29">
         <v>80</v>
       </c>
       <c r="CF11" s="34">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>45762</v>
       </c>
       <c r="CG11" s="34">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>46310</v>
       </c>
       <c r="CH11" s="29">
         <v>18</v>
       </c>
       <c r="CJ11" s="34">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>46311</v>
       </c>
       <c r="CK11" s="18">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>46311</v>
       </c>
       <c r="CL11" s="29">
@@ -9018,11 +9034,11 @@
         <v>46266</v>
       </c>
       <c r="CP11" s="79">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>46082</v>
       </c>
       <c r="CQ11" s="34">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>46143</v>
       </c>
       <c r="CR11" s="80">
@@ -9030,11 +9046,11 @@
       </c>
       <c r="CS11" s="73"/>
       <c r="CT11" s="79">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>46143</v>
       </c>
       <c r="CU11" s="34">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>46204</v>
       </c>
       <c r="CV11" s="80">
@@ -9042,11 +9058,11 @@
       </c>
       <c r="CW11" s="73"/>
       <c r="CX11" s="79">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>46204</v>
       </c>
       <c r="CY11" s="34">
-        <f t="shared" si="43"/>
+        <f t="shared" si="47"/>
         <v>46266</v>
       </c>
       <c r="CZ11" s="80">
@@ -9054,11 +9070,11 @@
       </c>
       <c r="DA11" s="73"/>
       <c r="DB11" s="79">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>46266</v>
       </c>
       <c r="DC11" s="34">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>46327</v>
       </c>
       <c r="DD11" s="80">
@@ -9066,11 +9082,11 @@
       </c>
       <c r="DE11" s="74"/>
       <c r="DF11" s="79">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>46327</v>
       </c>
       <c r="DG11" s="34">
-        <f t="shared" si="47"/>
+        <f t="shared" si="51"/>
         <v>46539</v>
       </c>
       <c r="DH11" s="80">
@@ -9237,47 +9253,51 @@
         <v>155</v>
       </c>
       <c r="BH12" s="18">
+        <f t="shared" si="27"/>
         <v>46198</v>
       </c>
       <c r="BI12" s="18">
+        <f t="shared" si="28"/>
         <v>46324</v>
       </c>
       <c r="BJ12" s="16">
         <v>90</v>
       </c>
       <c r="BL12" s="18">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>46325</v>
       </c>
       <c r="BM12" s="18">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>46476</v>
       </c>
       <c r="BN12" s="16">
         <v>5</v>
       </c>
       <c r="BP12" s="18">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>46280</v>
       </c>
       <c r="BQ12" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>46385</v>
       </c>
       <c r="BR12" s="16">
         <v>75</v>
       </c>
       <c r="BT12" s="18">
+        <f t="shared" si="33"/>
         <v>46386</v>
       </c>
       <c r="BU12" s="18">
+        <f t="shared" si="34"/>
         <v>46476</v>
       </c>
       <c r="BV12" s="16">
         <v>3</v>
       </c>
       <c r="BX12" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>46477</v>
       </c>
       <c r="BY12" s="18">
@@ -9288,33 +9308,33 @@
         <v>0</v>
       </c>
       <c r="CB12" s="22">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>45817</v>
       </c>
       <c r="CC12" s="22">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>45929</v>
       </c>
       <c r="CD12" s="16">
         <v>80</v>
       </c>
       <c r="CF12" s="22">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>45930</v>
       </c>
       <c r="CG12" s="22">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>46476</v>
       </c>
       <c r="CH12" s="16">
         <v>18</v>
       </c>
       <c r="CJ12" s="22">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>46477</v>
       </c>
       <c r="CK12" s="18">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>46477</v>
       </c>
       <c r="CL12" s="16">
@@ -9327,11 +9347,11 @@
         <v>46478</v>
       </c>
       <c r="CP12" s="77">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>46296</v>
       </c>
       <c r="CQ12" s="22">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>46357</v>
       </c>
       <c r="CR12" s="78">
@@ -9339,11 +9359,11 @@
       </c>
       <c r="CS12" s="73"/>
       <c r="CT12" s="77">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>46357</v>
       </c>
       <c r="CU12" s="22">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>46419</v>
       </c>
       <c r="CV12" s="78">
@@ -9351,11 +9371,11 @@
       </c>
       <c r="CW12" s="73"/>
       <c r="CX12" s="77">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>46419</v>
       </c>
       <c r="CY12" s="22">
-        <f t="shared" si="43"/>
+        <f t="shared" si="47"/>
         <v>46478</v>
       </c>
       <c r="CZ12" s="78">
@@ -9363,11 +9383,11 @@
       </c>
       <c r="DA12" s="73"/>
       <c r="DB12" s="77">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>46478</v>
       </c>
       <c r="DC12" s="22">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>46539</v>
       </c>
       <c r="DD12" s="78">
@@ -9375,11 +9395,11 @@
       </c>
       <c r="DE12" s="74"/>
       <c r="DF12" s="77">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>46539</v>
       </c>
       <c r="DG12" s="22">
-        <f t="shared" si="47"/>
+        <f t="shared" si="51"/>
         <v>46753</v>
       </c>
       <c r="DH12" s="78">
@@ -9546,47 +9566,51 @@
         <v>155</v>
       </c>
       <c r="BH13" s="31">
+        <f t="shared" si="27"/>
         <v>46408</v>
       </c>
       <c r="BI13" s="31">
+        <f t="shared" si="28"/>
         <v>46534</v>
       </c>
       <c r="BJ13" s="29">
         <v>90</v>
       </c>
       <c r="BL13" s="31">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>46535</v>
       </c>
       <c r="BM13" s="31">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>46688</v>
       </c>
       <c r="BN13" s="29">
         <v>5</v>
       </c>
       <c r="BP13" s="31">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>46490</v>
       </c>
       <c r="BQ13" s="31">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>46595</v>
       </c>
       <c r="BR13" s="29">
         <v>75</v>
       </c>
       <c r="BT13" s="31">
+        <f t="shared" si="33"/>
         <v>46596</v>
       </c>
       <c r="BU13" s="31">
+        <f t="shared" si="34"/>
         <v>46688</v>
       </c>
       <c r="BV13" s="29">
         <v>3</v>
       </c>
       <c r="BX13" s="31">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>46689</v>
       </c>
       <c r="BY13" s="31">
@@ -9597,33 +9621,33 @@
         <v>0</v>
       </c>
       <c r="CB13" s="34">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>46027</v>
       </c>
       <c r="CC13" s="34">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>46139</v>
       </c>
       <c r="CD13" s="29">
         <v>80</v>
       </c>
       <c r="CF13" s="34">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>46140</v>
       </c>
       <c r="CG13" s="34">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>46688</v>
       </c>
       <c r="CH13" s="29">
         <v>18</v>
       </c>
       <c r="CJ13" s="34">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>46689</v>
       </c>
       <c r="CK13" s="18">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>46689</v>
       </c>
       <c r="CL13" s="29">
@@ -9636,11 +9660,11 @@
         <v>46692</v>
       </c>
       <c r="CP13" s="79">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>46508</v>
       </c>
       <c r="CQ13" s="34">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>46569</v>
       </c>
       <c r="CR13" s="80">
@@ -9648,11 +9672,11 @@
       </c>
       <c r="CS13" s="73"/>
       <c r="CT13" s="79">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>46569</v>
       </c>
       <c r="CU13" s="34">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>46631</v>
       </c>
       <c r="CV13" s="80">
@@ -9660,11 +9684,11 @@
       </c>
       <c r="CW13" s="73"/>
       <c r="CX13" s="79">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>46631</v>
       </c>
       <c r="CY13" s="34">
-        <f t="shared" si="43"/>
+        <f t="shared" si="47"/>
         <v>46692</v>
       </c>
       <c r="CZ13" s="80">
@@ -9672,11 +9696,11 @@
       </c>
       <c r="DA13" s="73"/>
       <c r="DB13" s="79">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>46692</v>
       </c>
       <c r="DC13" s="34">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>46753</v>
       </c>
       <c r="DD13" s="80">
@@ -9684,11 +9708,11 @@
       </c>
       <c r="DE13" s="74"/>
       <c r="DF13" s="79">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>46753</v>
       </c>
       <c r="DG13" s="34">
-        <f t="shared" si="47"/>
+        <f t="shared" si="51"/>
         <v>46966</v>
       </c>
       <c r="DH13" s="80">
@@ -9855,47 +9879,51 @@
         <v>155</v>
       </c>
       <c r="BH14" s="18">
+        <f t="shared" si="27"/>
         <v>46638</v>
       </c>
       <c r="BI14" s="18">
+        <f t="shared" si="28"/>
         <v>46764</v>
       </c>
       <c r="BJ14" s="16">
         <v>90</v>
       </c>
       <c r="BL14" s="18">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>46765</v>
       </c>
       <c r="BM14" s="18">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>46917</v>
       </c>
       <c r="BN14" s="16">
         <v>5</v>
       </c>
       <c r="BP14" s="18">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>46717</v>
       </c>
       <c r="BQ14" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>46822</v>
       </c>
       <c r="BR14" s="16">
         <v>75</v>
       </c>
       <c r="BT14" s="18">
+        <f t="shared" si="33"/>
         <v>46825</v>
       </c>
       <c r="BU14" s="18">
+        <f t="shared" si="34"/>
         <v>46917</v>
       </c>
       <c r="BV14" s="16">
         <v>3</v>
       </c>
       <c r="BX14" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>46918</v>
       </c>
       <c r="BY14" s="18">
@@ -9906,33 +9934,33 @@
         <v>0</v>
       </c>
       <c r="CB14" s="22">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>46255</v>
       </c>
       <c r="CC14" s="22">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>46367</v>
       </c>
       <c r="CD14" s="16">
         <v>80</v>
       </c>
       <c r="CF14" s="22">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>46369</v>
       </c>
       <c r="CG14" s="22">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>46917</v>
       </c>
       <c r="CH14" s="16">
         <v>18</v>
       </c>
       <c r="CJ14" s="22">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>46918</v>
       </c>
       <c r="CK14" s="18">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>46918</v>
       </c>
       <c r="CL14" s="16">
@@ -9945,11 +9973,11 @@
         <v>46905</v>
       </c>
       <c r="CP14" s="77">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>46722</v>
       </c>
       <c r="CQ14" s="22">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>46784</v>
       </c>
       <c r="CR14" s="78">
@@ -9957,11 +9985,11 @@
       </c>
       <c r="CS14" s="73"/>
       <c r="CT14" s="77">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>46784</v>
       </c>
       <c r="CU14" s="22">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>46844</v>
       </c>
       <c r="CV14" s="78">
@@ -9969,11 +9997,11 @@
       </c>
       <c r="CW14" s="73"/>
       <c r="CX14" s="77">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>46844</v>
       </c>
       <c r="CY14" s="22">
-        <f t="shared" si="43"/>
+        <f t="shared" si="47"/>
         <v>46905</v>
       </c>
       <c r="CZ14" s="78">
@@ -9981,11 +10009,11 @@
       </c>
       <c r="DA14" s="73"/>
       <c r="DB14" s="77">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>46905</v>
       </c>
       <c r="DC14" s="22">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>46966</v>
       </c>
       <c r="DD14" s="78">
@@ -9993,11 +10021,11 @@
       </c>
       <c r="DE14" s="74"/>
       <c r="DF14" s="77">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>46966</v>
       </c>
       <c r="DG14" s="22">
-        <f t="shared" si="47"/>
+        <f t="shared" si="51"/>
         <v>47178</v>
       </c>
       <c r="DH14" s="78">
@@ -10164,47 +10192,51 @@
         <v>155</v>
       </c>
       <c r="BH15" s="31">
+        <f t="shared" si="27"/>
         <v>45741</v>
       </c>
       <c r="BI15" s="31">
+        <f t="shared" si="28"/>
         <v>45867</v>
       </c>
       <c r="BJ15" s="29">
         <v>90</v>
       </c>
       <c r="BL15" s="31">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>45868</v>
       </c>
       <c r="BM15" s="31">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>46021</v>
       </c>
       <c r="BN15" s="29">
         <v>5</v>
       </c>
       <c r="BP15" s="31">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>45824</v>
       </c>
       <c r="BQ15" s="31">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>45929</v>
       </c>
       <c r="BR15" s="29">
         <v>75</v>
       </c>
       <c r="BT15" s="31">
+        <f t="shared" si="33"/>
         <v>45930</v>
       </c>
       <c r="BU15" s="31">
+        <f t="shared" si="34"/>
         <v>46021</v>
       </c>
       <c r="BV15" s="29">
         <v>3</v>
       </c>
       <c r="BX15" s="31">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>46022</v>
       </c>
       <c r="BY15" s="31">
@@ -10215,33 +10247,33 @@
         <v>0</v>
       </c>
       <c r="CB15" s="34">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>45359</v>
       </c>
       <c r="CC15" s="34">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>45471</v>
       </c>
       <c r="CD15" s="29">
         <v>80</v>
       </c>
       <c r="CF15" s="34">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>45473</v>
       </c>
       <c r="CG15" s="34">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>46021</v>
       </c>
       <c r="CH15" s="29">
         <v>18</v>
       </c>
       <c r="CJ15" s="34">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>46022</v>
       </c>
       <c r="CK15" s="18">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>46022</v>
       </c>
       <c r="CL15" s="29">
@@ -10254,11 +10286,11 @@
         <v>45901</v>
       </c>
       <c r="CP15" s="79">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>45717</v>
       </c>
       <c r="CQ15" s="34">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>45778</v>
       </c>
       <c r="CR15" s="80">
@@ -10266,11 +10298,11 @@
       </c>
       <c r="CS15" s="73"/>
       <c r="CT15" s="79">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>45778</v>
       </c>
       <c r="CU15" s="34">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>45839</v>
       </c>
       <c r="CV15" s="80">
@@ -10278,11 +10310,11 @@
       </c>
       <c r="CW15" s="73"/>
       <c r="CX15" s="79">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>45839</v>
       </c>
       <c r="CY15" s="34">
-        <f t="shared" si="43"/>
+        <f t="shared" si="47"/>
         <v>45901</v>
       </c>
       <c r="CZ15" s="80">
@@ -10290,11 +10322,11 @@
       </c>
       <c r="DA15" s="73"/>
       <c r="DB15" s="79">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>45901</v>
       </c>
       <c r="DC15" s="34">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>45962</v>
       </c>
       <c r="DD15" s="80">
@@ -10302,11 +10334,11 @@
       </c>
       <c r="DE15" s="74"/>
       <c r="DF15" s="79">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>45962</v>
       </c>
       <c r="DG15" s="34">
-        <f t="shared" si="47"/>
+        <f t="shared" si="51"/>
         <v>46174</v>
       </c>
       <c r="DH15" s="80">
@@ -10473,47 +10505,51 @@
         <v>155</v>
       </c>
       <c r="BH16" s="18">
+        <f t="shared" si="27"/>
         <v>46577</v>
       </c>
       <c r="BI16" s="18">
+        <f t="shared" si="28"/>
         <v>46703</v>
       </c>
       <c r="BJ16" s="16">
         <v>90</v>
       </c>
       <c r="BL16" s="18">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>46704</v>
       </c>
       <c r="BM16" s="18">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>46856</v>
       </c>
       <c r="BN16" s="16">
         <v>5</v>
       </c>
       <c r="BP16" s="18">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>46659</v>
       </c>
       <c r="BQ16" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>46764</v>
       </c>
       <c r="BR16" s="16">
         <v>75</v>
       </c>
       <c r="BT16" s="18">
+        <f t="shared" si="33"/>
         <v>46765</v>
       </c>
       <c r="BU16" s="18">
+        <f t="shared" si="34"/>
         <v>46856</v>
       </c>
       <c r="BV16" s="16">
         <v>3</v>
       </c>
       <c r="BX16" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>46857</v>
       </c>
       <c r="BY16" s="18">
@@ -10524,33 +10560,33 @@
         <v>0</v>
       </c>
       <c r="CB16" s="22">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>46195</v>
       </c>
       <c r="CC16" s="22">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>46307</v>
       </c>
       <c r="CD16" s="16">
         <v>80</v>
       </c>
       <c r="CF16" s="22">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>46308</v>
       </c>
       <c r="CG16" s="22">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>46856</v>
       </c>
       <c r="CH16" s="16">
         <v>18</v>
       </c>
       <c r="CJ16" s="22">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>46857</v>
       </c>
       <c r="CK16" s="18">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>46857</v>
       </c>
       <c r="CL16" s="16">
@@ -10563,11 +10599,11 @@
         <v>46874</v>
       </c>
       <c r="CP16" s="77">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>46692</v>
       </c>
       <c r="CQ16" s="22">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>46753</v>
       </c>
       <c r="CR16" s="78">
@@ -10575,11 +10611,11 @@
       </c>
       <c r="CS16" s="73"/>
       <c r="CT16" s="77">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>46753</v>
       </c>
       <c r="CU16" s="22">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>46813</v>
       </c>
       <c r="CV16" s="78">
@@ -10587,11 +10623,11 @@
       </c>
       <c r="CW16" s="73"/>
       <c r="CX16" s="77">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>46813</v>
       </c>
       <c r="CY16" s="22">
-        <f t="shared" si="43"/>
+        <f t="shared" si="47"/>
         <v>46874</v>
       </c>
       <c r="CZ16" s="78">
@@ -10599,11 +10635,11 @@
       </c>
       <c r="DA16" s="73"/>
       <c r="DB16" s="77">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>46874</v>
       </c>
       <c r="DC16" s="22">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>46935</v>
       </c>
       <c r="DD16" s="78">
@@ -10611,11 +10647,11 @@
       </c>
       <c r="DE16" s="74"/>
       <c r="DF16" s="77">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>46935</v>
       </c>
       <c r="DG16" s="22">
-        <f t="shared" si="47"/>
+        <f t="shared" si="51"/>
         <v>47150</v>
       </c>
       <c r="DH16" s="78">
@@ -10782,47 +10818,51 @@
         <v>155</v>
       </c>
       <c r="BH17" s="31">
+        <f t="shared" si="27"/>
         <v>47855</v>
       </c>
       <c r="BI17" s="31">
+        <f t="shared" si="28"/>
         <v>47981</v>
       </c>
       <c r="BJ17" s="29">
         <v>90</v>
       </c>
       <c r="BL17" s="31">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>47982</v>
       </c>
       <c r="BM17" s="31">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>48135</v>
       </c>
       <c r="BN17" s="29">
         <v>5</v>
       </c>
       <c r="BP17" s="31">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>47935</v>
       </c>
       <c r="BQ17" s="31">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>48040</v>
       </c>
       <c r="BR17" s="29">
         <v>75</v>
       </c>
       <c r="BT17" s="31">
+        <f t="shared" si="33"/>
         <v>48043</v>
       </c>
       <c r="BU17" s="31">
+        <f t="shared" si="34"/>
         <v>48135</v>
       </c>
       <c r="BV17" s="29">
         <v>3</v>
       </c>
       <c r="BX17" s="31">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>48136</v>
       </c>
       <c r="BY17" s="31">
@@ -10833,33 +10873,33 @@
         <v>0</v>
       </c>
       <c r="CB17" s="34">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>47473</v>
       </c>
       <c r="CC17" s="34">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>47585</v>
       </c>
       <c r="CD17" s="29">
         <v>80</v>
       </c>
       <c r="CF17" s="34">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>47587</v>
       </c>
       <c r="CG17" s="34">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>48135</v>
       </c>
       <c r="CH17" s="29">
         <v>18</v>
       </c>
       <c r="CJ17" s="34">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>48136</v>
       </c>
       <c r="CK17" s="18">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>48136</v>
       </c>
       <c r="CL17" s="29">
@@ -10872,11 +10912,11 @@
         <v>48153</v>
       </c>
       <c r="CP17" s="79">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>47969</v>
       </c>
       <c r="CQ17" s="34">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>48030</v>
       </c>
       <c r="CR17" s="80">
@@ -10884,11 +10924,11 @@
       </c>
       <c r="CS17" s="73"/>
       <c r="CT17" s="79">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>48030</v>
       </c>
       <c r="CU17" s="34">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>48092</v>
       </c>
       <c r="CV17" s="80">
@@ -10896,11 +10936,11 @@
       </c>
       <c r="CW17" s="73"/>
       <c r="CX17" s="79">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>48092</v>
       </c>
       <c r="CY17" s="34">
-        <f t="shared" si="43"/>
+        <f t="shared" si="47"/>
         <v>48153</v>
       </c>
       <c r="CZ17" s="80">
@@ -10908,11 +10948,11 @@
       </c>
       <c r="DA17" s="73"/>
       <c r="DB17" s="79">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>48153</v>
       </c>
       <c r="DC17" s="34">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>48214</v>
       </c>
       <c r="DD17" s="80">
@@ -10920,11 +10960,11 @@
       </c>
       <c r="DE17" s="74"/>
       <c r="DF17" s="79">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>48214</v>
       </c>
       <c r="DG17" s="34">
-        <f t="shared" si="47"/>
+        <f t="shared" si="51"/>
         <v>48427</v>
       </c>
       <c r="DH17" s="80">
@@ -10957,7 +10997,7 @@
         <v>45838</v>
       </c>
       <c r="K18" s="18">
-        <f t="shared" ref="K18:K30" si="48">WORKDAY(N18,-1)</f>
+        <f t="shared" ref="K18:K30" si="52">WORKDAY(N18,-1)</f>
         <v>46386</v>
       </c>
       <c r="L18" s="16">
@@ -10968,7 +11008,7 @@
         <v>46387</v>
       </c>
       <c r="O18" s="18">
-        <f t="shared" ref="O18:O30" si="49">WORKDAY(Q18,-1)</f>
+        <f t="shared" ref="O18:O30" si="53">WORKDAY(Q18,-1)</f>
         <v>46387</v>
       </c>
       <c r="P18" s="20">
@@ -11091,47 +11131,51 @@
         <v>155</v>
       </c>
       <c r="BH18" s="18">
+        <f t="shared" si="27"/>
         <v>46106</v>
       </c>
       <c r="BI18" s="18">
+        <f t="shared" si="28"/>
         <v>46232</v>
       </c>
       <c r="BJ18" s="16">
         <v>90</v>
       </c>
       <c r="BL18" s="18">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>46233</v>
       </c>
       <c r="BM18" s="18">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>46386</v>
       </c>
       <c r="BN18" s="16">
         <v>5</v>
       </c>
       <c r="BP18" s="18">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>46189</v>
       </c>
       <c r="BQ18" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>46294</v>
       </c>
       <c r="BR18" s="16">
         <v>75</v>
       </c>
       <c r="BT18" s="18">
+        <f t="shared" si="33"/>
         <v>46295</v>
       </c>
       <c r="BU18" s="18">
+        <f t="shared" si="34"/>
         <v>46386</v>
       </c>
       <c r="BV18" s="16">
         <v>3</v>
       </c>
       <c r="BX18" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>46387</v>
       </c>
       <c r="BY18" s="18">
@@ -11142,33 +11186,33 @@
         <v>0</v>
       </c>
       <c r="CB18" s="22">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>45723</v>
       </c>
       <c r="CC18" s="22">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>45835</v>
       </c>
       <c r="CD18" s="16">
         <v>80</v>
       </c>
       <c r="CF18" s="22">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>45838</v>
       </c>
       <c r="CG18" s="22">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>46386</v>
       </c>
       <c r="CH18" s="16">
         <v>18</v>
       </c>
       <c r="CJ18" s="22">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>46387</v>
       </c>
       <c r="CK18" s="18">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>46387</v>
       </c>
       <c r="CL18" s="16">
@@ -11181,11 +11225,11 @@
         <v>46388</v>
       </c>
       <c r="CP18" s="77">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>46204</v>
       </c>
       <c r="CQ18" s="22">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>46266</v>
       </c>
       <c r="CR18" s="78">
@@ -11193,11 +11237,11 @@
       </c>
       <c r="CS18" s="73"/>
       <c r="CT18" s="77">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>46266</v>
       </c>
       <c r="CU18" s="22">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>46327</v>
       </c>
       <c r="CV18" s="78">
@@ -11205,11 +11249,11 @@
       </c>
       <c r="CW18" s="73"/>
       <c r="CX18" s="77">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>46327</v>
       </c>
       <c r="CY18" s="22">
-        <f t="shared" si="43"/>
+        <f t="shared" si="47"/>
         <v>46388</v>
       </c>
       <c r="CZ18" s="78">
@@ -11217,11 +11261,11 @@
       </c>
       <c r="DA18" s="73"/>
       <c r="DB18" s="77">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>46388</v>
       </c>
       <c r="DC18" s="22">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>46447</v>
       </c>
       <c r="DD18" s="78">
@@ -11229,11 +11273,11 @@
       </c>
       <c r="DE18" s="74"/>
       <c r="DF18" s="77">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>46447</v>
       </c>
       <c r="DG18" s="22">
-        <f t="shared" si="47"/>
+        <f t="shared" si="51"/>
         <v>46661</v>
       </c>
       <c r="DH18" s="78">
@@ -11266,7 +11310,7 @@
         <v>45350</v>
       </c>
       <c r="K19" s="31">
-        <f t="shared" si="48"/>
+        <f t="shared" si="52"/>
         <v>45897</v>
       </c>
       <c r="L19" s="29">
@@ -11277,7 +11321,7 @@
         <v>45898</v>
       </c>
       <c r="O19" s="31">
-        <f t="shared" si="49"/>
+        <f t="shared" si="53"/>
         <v>45898</v>
       </c>
       <c r="P19" s="33">
@@ -11400,47 +11444,51 @@
         <v>155</v>
       </c>
       <c r="BH19" s="31">
+        <f t="shared" si="27"/>
         <v>45555</v>
       </c>
       <c r="BI19" s="31">
+        <f t="shared" si="28"/>
         <v>45681</v>
       </c>
       <c r="BJ19" s="29">
         <v>90</v>
       </c>
       <c r="BL19" s="31">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>45683</v>
       </c>
       <c r="BM19" s="31">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>45834</v>
       </c>
       <c r="BN19" s="29">
         <v>5</v>
       </c>
       <c r="BP19" s="31">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>45636</v>
       </c>
       <c r="BQ19" s="31">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>45741</v>
       </c>
       <c r="BR19" s="29">
         <v>75</v>
       </c>
       <c r="BT19" s="31">
+        <f t="shared" si="33"/>
         <v>45742</v>
       </c>
       <c r="BU19" s="31">
+        <f t="shared" si="34"/>
         <v>45834</v>
       </c>
       <c r="BV19" s="29">
         <v>3</v>
       </c>
       <c r="BX19" s="31">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>45835</v>
       </c>
       <c r="BY19" s="31">
@@ -11451,33 +11499,33 @@
         <v>0</v>
       </c>
       <c r="CB19" s="34">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>45173</v>
       </c>
       <c r="CC19" s="34">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>45285</v>
       </c>
       <c r="CD19" s="29">
         <v>80</v>
       </c>
       <c r="CF19" s="34">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>45286</v>
       </c>
       <c r="CG19" s="34">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>45834</v>
       </c>
       <c r="CH19" s="29">
         <v>18</v>
       </c>
       <c r="CJ19" s="34">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>45835</v>
       </c>
       <c r="CK19" s="18">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>45835</v>
       </c>
       <c r="CL19" s="29">
@@ -11490,11 +11538,11 @@
         <v>45901</v>
       </c>
       <c r="CP19" s="79">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>45717</v>
       </c>
       <c r="CQ19" s="34">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>45778</v>
       </c>
       <c r="CR19" s="80">
@@ -11502,11 +11550,11 @@
       </c>
       <c r="CS19" s="73"/>
       <c r="CT19" s="79">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>45778</v>
       </c>
       <c r="CU19" s="34">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>45839</v>
       </c>
       <c r="CV19" s="80">
@@ -11514,11 +11562,11 @@
       </c>
       <c r="CW19" s="73"/>
       <c r="CX19" s="79">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>45839</v>
       </c>
       <c r="CY19" s="34">
-        <f t="shared" si="43"/>
+        <f t="shared" si="47"/>
         <v>45901</v>
       </c>
       <c r="CZ19" s="80">
@@ -11526,11 +11574,11 @@
       </c>
       <c r="DA19" s="73"/>
       <c r="DB19" s="79">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>45901</v>
       </c>
       <c r="DC19" s="34">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>45962</v>
       </c>
       <c r="DD19" s="80">
@@ -11538,11 +11586,11 @@
       </c>
       <c r="DE19" s="74"/>
       <c r="DF19" s="79">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>45962</v>
       </c>
       <c r="DG19" s="34">
-        <f t="shared" si="47"/>
+        <f t="shared" si="51"/>
         <v>46174</v>
       </c>
       <c r="DH19" s="80">
@@ -11575,7 +11623,7 @@
         <v>45687</v>
       </c>
       <c r="K20" s="18">
-        <f t="shared" si="48"/>
+        <f t="shared" si="52"/>
         <v>46233</v>
       </c>
       <c r="L20" s="16">
@@ -11586,7 +11634,7 @@
         <v>46234</v>
       </c>
       <c r="O20" s="18">
-        <f t="shared" si="49"/>
+        <f t="shared" si="53"/>
         <v>46234</v>
       </c>
       <c r="P20" s="20">
@@ -11709,47 +11757,51 @@
         <v>155</v>
       </c>
       <c r="BH20" s="18">
+        <f t="shared" si="27"/>
         <v>46008</v>
       </c>
       <c r="BI20" s="18">
+        <f t="shared" si="28"/>
         <v>46134</v>
       </c>
       <c r="BJ20" s="16">
         <v>90</v>
       </c>
       <c r="BL20" s="18">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>46135</v>
       </c>
       <c r="BM20" s="18">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>46288</v>
       </c>
       <c r="BN20" s="16">
         <v>5</v>
       </c>
       <c r="BP20" s="18">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>46090</v>
       </c>
       <c r="BQ20" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>46195</v>
       </c>
       <c r="BR20" s="16">
         <v>75</v>
       </c>
       <c r="BT20" s="18">
+        <f t="shared" si="33"/>
         <v>46196</v>
       </c>
       <c r="BU20" s="18">
+        <f t="shared" si="34"/>
         <v>46288</v>
       </c>
       <c r="BV20" s="16">
         <v>3</v>
       </c>
       <c r="BX20" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>46289</v>
       </c>
       <c r="BY20" s="18">
@@ -11760,33 +11812,33 @@
         <v>0</v>
       </c>
       <c r="CB20" s="22">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>45625</v>
       </c>
       <c r="CC20" s="22">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>45737</v>
       </c>
       <c r="CD20" s="16">
         <v>80</v>
       </c>
       <c r="CF20" s="22">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>45739</v>
       </c>
       <c r="CG20" s="22">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>46288</v>
       </c>
       <c r="CH20" s="16">
         <v>18</v>
       </c>
       <c r="CJ20" s="22">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>46289</v>
       </c>
       <c r="CK20" s="18">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>46289</v>
       </c>
       <c r="CL20" s="16">
@@ -11799,11 +11851,11 @@
         <v>46235</v>
       </c>
       <c r="CP20" s="77">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>46054</v>
       </c>
       <c r="CQ20" s="22">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>46113</v>
       </c>
       <c r="CR20" s="78">
@@ -11811,11 +11863,11 @@
       </c>
       <c r="CS20" s="73"/>
       <c r="CT20" s="77">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>46113</v>
       </c>
       <c r="CU20" s="22">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>46174</v>
       </c>
       <c r="CV20" s="78">
@@ -11823,11 +11875,11 @@
       </c>
       <c r="CW20" s="73"/>
       <c r="CX20" s="77">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>46174</v>
       </c>
       <c r="CY20" s="22">
-        <f t="shared" si="43"/>
+        <f t="shared" si="47"/>
         <v>46235</v>
       </c>
       <c r="CZ20" s="78">
@@ -11835,11 +11887,11 @@
       </c>
       <c r="DA20" s="73"/>
       <c r="DB20" s="77">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>46235</v>
       </c>
       <c r="DC20" s="22">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>46296</v>
       </c>
       <c r="DD20" s="78">
@@ -11847,11 +11899,11 @@
       </c>
       <c r="DE20" s="74"/>
       <c r="DF20" s="77">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>46296</v>
       </c>
       <c r="DG20" s="22">
-        <f t="shared" si="47"/>
+        <f t="shared" si="51"/>
         <v>46508</v>
       </c>
       <c r="DH20" s="78">
@@ -11884,7 +11936,7 @@
         <v>46110</v>
       </c>
       <c r="K21" s="31">
-        <f t="shared" si="48"/>
+        <f t="shared" si="52"/>
         <v>46659</v>
       </c>
       <c r="L21" s="29">
@@ -11895,7 +11947,7 @@
         <v>46660</v>
       </c>
       <c r="O21" s="31">
-        <f t="shared" si="49"/>
+        <f t="shared" si="53"/>
         <v>46660</v>
       </c>
       <c r="P21" s="33">
@@ -12018,47 +12070,51 @@
         <v>155</v>
       </c>
       <c r="BH21" s="31">
+        <f t="shared" si="27"/>
         <v>46349</v>
       </c>
       <c r="BI21" s="31">
+        <f t="shared" si="28"/>
         <v>46475</v>
       </c>
       <c r="BJ21" s="29">
         <v>90</v>
       </c>
       <c r="BL21" s="31">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>46476</v>
       </c>
       <c r="BM21" s="31">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>46629</v>
       </c>
       <c r="BN21" s="29">
         <v>5</v>
       </c>
       <c r="BP21" s="31">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>46430</v>
       </c>
       <c r="BQ21" s="31">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>46535</v>
       </c>
       <c r="BR21" s="29">
         <v>75</v>
       </c>
       <c r="BT21" s="31">
+        <f t="shared" si="33"/>
         <v>46537</v>
       </c>
       <c r="BU21" s="31">
+        <f t="shared" si="34"/>
         <v>46629</v>
       </c>
       <c r="BV21" s="29">
         <v>3</v>
       </c>
       <c r="BX21" s="31">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>46630</v>
       </c>
       <c r="BY21" s="31">
@@ -12069,33 +12125,33 @@
         <v>0</v>
       </c>
       <c r="CB21" s="34">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>45968</v>
       </c>
       <c r="CC21" s="34">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>46080</v>
       </c>
       <c r="CD21" s="29">
         <v>80</v>
       </c>
       <c r="CF21" s="34">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>46081</v>
       </c>
       <c r="CG21" s="34">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>46629</v>
       </c>
       <c r="CH21" s="29">
         <v>18</v>
       </c>
       <c r="CJ21" s="34">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>46630</v>
       </c>
       <c r="CK21" s="18">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>46630</v>
       </c>
       <c r="CL21" s="29">
@@ -12108,11 +12164,11 @@
         <v>46661</v>
       </c>
       <c r="CP21" s="79">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>46478</v>
       </c>
       <c r="CQ21" s="34">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>46539</v>
       </c>
       <c r="CR21" s="80">
@@ -12120,11 +12176,11 @@
       </c>
       <c r="CS21" s="73"/>
       <c r="CT21" s="79">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>46539</v>
       </c>
       <c r="CU21" s="34">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>46600</v>
       </c>
       <c r="CV21" s="80">
@@ -12132,11 +12188,11 @@
       </c>
       <c r="CW21" s="73"/>
       <c r="CX21" s="79">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>46600</v>
       </c>
       <c r="CY21" s="34">
-        <f t="shared" si="43"/>
+        <f t="shared" si="47"/>
         <v>46661</v>
       </c>
       <c r="CZ21" s="80">
@@ -12144,11 +12200,11 @@
       </c>
       <c r="DA21" s="73"/>
       <c r="DB21" s="79">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>46661</v>
       </c>
       <c r="DC21" s="34">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>46722</v>
       </c>
       <c r="DD21" s="80">
@@ -12156,11 +12212,11 @@
       </c>
       <c r="DE21" s="74"/>
       <c r="DF21" s="79">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>46722</v>
       </c>
       <c r="DG21" s="34">
-        <f t="shared" si="47"/>
+        <f t="shared" si="51"/>
         <v>46935</v>
       </c>
       <c r="DH21" s="80">
@@ -12193,7 +12249,7 @@
         <v>46322</v>
       </c>
       <c r="K22" s="18">
-        <f t="shared" si="48"/>
+        <f t="shared" si="52"/>
         <v>46870</v>
       </c>
       <c r="L22" s="16">
@@ -12204,7 +12260,7 @@
         <v>46871</v>
       </c>
       <c r="O22" s="18">
-        <f t="shared" si="49"/>
+        <f t="shared" si="53"/>
         <v>46871</v>
       </c>
       <c r="P22" s="20">
@@ -12327,47 +12383,51 @@
         <v>155</v>
       </c>
       <c r="BH22" s="18">
+        <f t="shared" si="27"/>
         <v>46563</v>
       </c>
       <c r="BI22" s="18">
+        <f t="shared" si="28"/>
         <v>46689</v>
       </c>
       <c r="BJ22" s="16">
         <v>90</v>
       </c>
       <c r="BL22" s="18">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>46690</v>
       </c>
       <c r="BM22" s="18">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>46842</v>
       </c>
       <c r="BN22" s="16">
         <v>5</v>
       </c>
       <c r="BP22" s="18">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>46645</v>
       </c>
       <c r="BQ22" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>46750</v>
       </c>
       <c r="BR22" s="16">
         <v>75</v>
       </c>
       <c r="BT22" s="18">
+        <f t="shared" si="33"/>
         <v>46751</v>
       </c>
       <c r="BU22" s="18">
+        <f t="shared" si="34"/>
         <v>46842</v>
       </c>
       <c r="BV22" s="16">
         <v>3</v>
       </c>
       <c r="BX22" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>46843</v>
       </c>
       <c r="BY22" s="18">
@@ -12378,33 +12438,33 @@
         <v>0</v>
       </c>
       <c r="CB22" s="22">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>46182</v>
       </c>
       <c r="CC22" s="22">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>46294</v>
       </c>
       <c r="CD22" s="16">
         <v>80</v>
       </c>
       <c r="CF22" s="22">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>46295</v>
       </c>
       <c r="CG22" s="22">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>46842</v>
       </c>
       <c r="CH22" s="16">
         <v>18</v>
       </c>
       <c r="CJ22" s="22">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>46843</v>
       </c>
       <c r="CK22" s="18">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>46843</v>
       </c>
       <c r="CL22" s="16">
@@ -12417,11 +12477,11 @@
         <v>46874</v>
       </c>
       <c r="CP22" s="77">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>46692</v>
       </c>
       <c r="CQ22" s="22">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>46753</v>
       </c>
       <c r="CR22" s="78">
@@ -12429,11 +12489,11 @@
       </c>
       <c r="CS22" s="73"/>
       <c r="CT22" s="77">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>46753</v>
       </c>
       <c r="CU22" s="22">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>46813</v>
       </c>
       <c r="CV22" s="78">
@@ -12441,11 +12501,11 @@
       </c>
       <c r="CW22" s="73"/>
       <c r="CX22" s="77">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>46813</v>
       </c>
       <c r="CY22" s="22">
-        <f t="shared" si="43"/>
+        <f t="shared" si="47"/>
         <v>46874</v>
       </c>
       <c r="CZ22" s="78">
@@ -12453,11 +12513,11 @@
       </c>
       <c r="DA22" s="73"/>
       <c r="DB22" s="77">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>46874</v>
       </c>
       <c r="DC22" s="22">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>46935</v>
       </c>
       <c r="DD22" s="78">
@@ -12465,11 +12525,11 @@
       </c>
       <c r="DE22" s="74"/>
       <c r="DF22" s="77">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>46935</v>
       </c>
       <c r="DG22" s="22">
-        <f t="shared" si="47"/>
+        <f t="shared" si="51"/>
         <v>47150</v>
       </c>
       <c r="DH22" s="78">
@@ -12502,7 +12562,7 @@
         <v>45838</v>
       </c>
       <c r="K23" s="31">
-        <f t="shared" si="48"/>
+        <f t="shared" si="52"/>
         <v>46386</v>
       </c>
       <c r="L23" s="29">
@@ -12513,7 +12573,7 @@
         <v>46387</v>
       </c>
       <c r="O23" s="31">
-        <f t="shared" si="49"/>
+        <f t="shared" si="53"/>
         <v>46387</v>
       </c>
       <c r="P23" s="33">
@@ -12636,47 +12696,51 @@
         <v>155</v>
       </c>
       <c r="BH23" s="31">
+        <f t="shared" si="27"/>
         <v>46106</v>
       </c>
       <c r="BI23" s="31">
+        <f t="shared" si="28"/>
         <v>46232</v>
       </c>
       <c r="BJ23" s="29">
         <v>90</v>
       </c>
       <c r="BL23" s="31">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>46233</v>
       </c>
       <c r="BM23" s="31">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>46386</v>
       </c>
       <c r="BN23" s="29">
         <v>5</v>
       </c>
       <c r="BP23" s="31">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>46189</v>
       </c>
       <c r="BQ23" s="31">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>46294</v>
       </c>
       <c r="BR23" s="29">
         <v>75</v>
       </c>
       <c r="BT23" s="31">
+        <f t="shared" si="33"/>
         <v>46295</v>
       </c>
       <c r="BU23" s="31">
+        <f t="shared" si="34"/>
         <v>46386</v>
       </c>
       <c r="BV23" s="29">
         <v>3</v>
       </c>
       <c r="BX23" s="31">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>46387</v>
       </c>
       <c r="BY23" s="31">
@@ -12687,33 +12751,33 @@
         <v>0</v>
       </c>
       <c r="CB23" s="34">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>45723</v>
       </c>
       <c r="CC23" s="34">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>45835</v>
       </c>
       <c r="CD23" s="29">
         <v>80</v>
       </c>
       <c r="CF23" s="34">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>45838</v>
       </c>
       <c r="CG23" s="34">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>46386</v>
       </c>
       <c r="CH23" s="29">
         <v>18</v>
       </c>
       <c r="CJ23" s="34">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>46387</v>
       </c>
       <c r="CK23" s="18">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>46387</v>
       </c>
       <c r="CL23" s="29">
@@ -12726,11 +12790,11 @@
         <v>46388</v>
       </c>
       <c r="CP23" s="79">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>46204</v>
       </c>
       <c r="CQ23" s="34">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>46266</v>
       </c>
       <c r="CR23" s="80">
@@ -12738,11 +12802,11 @@
       </c>
       <c r="CS23" s="73"/>
       <c r="CT23" s="79">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>46266</v>
       </c>
       <c r="CU23" s="34">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>46327</v>
       </c>
       <c r="CV23" s="80">
@@ -12750,11 +12814,11 @@
       </c>
       <c r="CW23" s="73"/>
       <c r="CX23" s="79">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>46327</v>
       </c>
       <c r="CY23" s="34">
-        <f t="shared" si="43"/>
+        <f t="shared" si="47"/>
         <v>46388</v>
       </c>
       <c r="CZ23" s="80">
@@ -12762,11 +12826,11 @@
       </c>
       <c r="DA23" s="73"/>
       <c r="DB23" s="79">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>46388</v>
       </c>
       <c r="DC23" s="34">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>46447</v>
       </c>
       <c r="DD23" s="80">
@@ -12774,11 +12838,11 @@
       </c>
       <c r="DE23" s="74"/>
       <c r="DF23" s="79">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>46447</v>
       </c>
       <c r="DG23" s="34">
-        <f t="shared" si="47"/>
+        <f t="shared" si="51"/>
         <v>46661</v>
       </c>
       <c r="DH23" s="80">
@@ -12945,47 +13009,51 @@
         <v>155</v>
       </c>
       <c r="BH24" s="18">
+        <f t="shared" si="27"/>
         <v>45741</v>
       </c>
       <c r="BI24" s="18">
+        <f t="shared" si="28"/>
         <v>45867</v>
       </c>
       <c r="BJ24" s="16">
         <v>90</v>
       </c>
       <c r="BL24" s="18">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>45868</v>
       </c>
       <c r="BM24" s="18">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>46021</v>
       </c>
       <c r="BN24" s="16">
         <v>5</v>
       </c>
       <c r="BP24" s="18">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>45824</v>
       </c>
       <c r="BQ24" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>45929</v>
       </c>
       <c r="BR24" s="16">
         <v>75</v>
       </c>
       <c r="BT24" s="18">
+        <f t="shared" si="33"/>
         <v>45930</v>
       </c>
       <c r="BU24" s="18">
+        <f t="shared" si="34"/>
         <v>46021</v>
       </c>
       <c r="BV24" s="16">
         <v>3</v>
       </c>
       <c r="BX24" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>46022</v>
       </c>
       <c r="BY24" s="18">
@@ -12996,33 +13064,33 @@
         <v>0</v>
       </c>
       <c r="CB24" s="22">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>45359</v>
       </c>
       <c r="CC24" s="22">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>45471</v>
       </c>
       <c r="CD24" s="16">
         <v>80</v>
       </c>
       <c r="CF24" s="22">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>45473</v>
       </c>
       <c r="CG24" s="22">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>46021</v>
       </c>
       <c r="CH24" s="16">
         <v>18</v>
       </c>
       <c r="CJ24" s="22">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>46022</v>
       </c>
       <c r="CK24" s="18">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>46022</v>
       </c>
       <c r="CL24" s="16">
@@ -13035,11 +13103,11 @@
         <v>45901</v>
       </c>
       <c r="CP24" s="77">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>45717</v>
       </c>
       <c r="CQ24" s="22">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>45778</v>
       </c>
       <c r="CR24" s="78">
@@ -13047,11 +13115,11 @@
       </c>
       <c r="CS24" s="73"/>
       <c r="CT24" s="77">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>45778</v>
       </c>
       <c r="CU24" s="22">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>45839</v>
       </c>
       <c r="CV24" s="78">
@@ -13059,11 +13127,11 @@
       </c>
       <c r="CW24" s="73"/>
       <c r="CX24" s="77">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>45839</v>
       </c>
       <c r="CY24" s="22">
-        <f t="shared" si="43"/>
+        <f t="shared" si="47"/>
         <v>45901</v>
       </c>
       <c r="CZ24" s="78">
@@ -13071,11 +13139,11 @@
       </c>
       <c r="DA24" s="73"/>
       <c r="DB24" s="77">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>45901</v>
       </c>
       <c r="DC24" s="22">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>45962</v>
       </c>
       <c r="DD24" s="78">
@@ -13083,11 +13151,11 @@
       </c>
       <c r="DE24" s="74"/>
       <c r="DF24" s="77">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>45962</v>
       </c>
       <c r="DG24" s="22">
-        <f t="shared" si="47"/>
+        <f t="shared" si="51"/>
         <v>46174</v>
       </c>
       <c r="DH24" s="78">
@@ -13254,47 +13322,51 @@
         <v>155</v>
       </c>
       <c r="BH25" s="31">
+        <f t="shared" si="27"/>
         <v>46135</v>
       </c>
       <c r="BI25" s="31">
+        <f t="shared" si="28"/>
         <v>46261</v>
       </c>
       <c r="BJ25" s="29">
         <v>90</v>
       </c>
       <c r="BL25" s="31">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>46262</v>
       </c>
       <c r="BM25" s="31">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>46415</v>
       </c>
       <c r="BN25" s="29">
         <v>5</v>
       </c>
       <c r="BP25" s="31">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>46217</v>
       </c>
       <c r="BQ25" s="31">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>46322</v>
       </c>
       <c r="BR25" s="29">
         <v>75</v>
       </c>
       <c r="BT25" s="31">
+        <f t="shared" si="33"/>
         <v>46323</v>
       </c>
       <c r="BU25" s="31">
+        <f t="shared" si="34"/>
         <v>46415</v>
       </c>
       <c r="BV25" s="29">
         <v>3</v>
       </c>
       <c r="BX25" s="31">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>46416</v>
       </c>
       <c r="BY25" s="31">
@@ -13305,33 +13377,33 @@
         <v>0</v>
       </c>
       <c r="CB25" s="34">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>45751</v>
       </c>
       <c r="CC25" s="34">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>45863</v>
       </c>
       <c r="CD25" s="29">
         <v>80</v>
       </c>
       <c r="CF25" s="34">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>45866</v>
       </c>
       <c r="CG25" s="34">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>46415</v>
       </c>
       <c r="CH25" s="29">
         <v>18</v>
       </c>
       <c r="CJ25" s="34">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>46416</v>
       </c>
       <c r="CK25" s="18">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>46416</v>
       </c>
       <c r="CL25" s="29">
@@ -13344,11 +13416,11 @@
         <v>46447</v>
       </c>
       <c r="CP25" s="79">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>46266</v>
       </c>
       <c r="CQ25" s="34">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>46327</v>
       </c>
       <c r="CR25" s="80">
@@ -13356,11 +13428,11 @@
       </c>
       <c r="CS25" s="73"/>
       <c r="CT25" s="79">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>46327</v>
       </c>
       <c r="CU25" s="34">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>46388</v>
       </c>
       <c r="CV25" s="80">
@@ -13368,11 +13440,11 @@
       </c>
       <c r="CW25" s="73"/>
       <c r="CX25" s="79">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>46388</v>
       </c>
       <c r="CY25" s="34">
-        <f t="shared" si="43"/>
+        <f t="shared" si="47"/>
         <v>46447</v>
       </c>
       <c r="CZ25" s="80">
@@ -13380,11 +13452,11 @@
       </c>
       <c r="DA25" s="73"/>
       <c r="DB25" s="79">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>46447</v>
       </c>
       <c r="DC25" s="34">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>46508</v>
       </c>
       <c r="DD25" s="80">
@@ -13392,11 +13464,11 @@
       </c>
       <c r="DE25" s="74"/>
       <c r="DF25" s="79">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>46508</v>
       </c>
       <c r="DG25" s="34">
-        <f t="shared" si="47"/>
+        <f t="shared" si="51"/>
         <v>46722</v>
       </c>
       <c r="DH25" s="80">
@@ -13429,7 +13501,7 @@
         <v>45350</v>
       </c>
       <c r="K26" s="18">
-        <f t="shared" si="48"/>
+        <f t="shared" si="52"/>
         <v>45897</v>
       </c>
       <c r="L26" s="16">
@@ -13440,7 +13512,7 @@
         <v>45898</v>
       </c>
       <c r="O26" s="18">
-        <f t="shared" si="49"/>
+        <f t="shared" si="53"/>
         <v>45898</v>
       </c>
       <c r="P26" s="20">
@@ -13563,47 +13635,51 @@
         <v>155</v>
       </c>
       <c r="BH26" s="18">
+        <f t="shared" si="27"/>
         <v>45741</v>
       </c>
       <c r="BI26" s="18">
+        <f t="shared" si="28"/>
         <v>45867</v>
       </c>
       <c r="BJ26" s="16">
         <v>90</v>
       </c>
       <c r="BL26" s="18">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>45868</v>
       </c>
       <c r="BM26" s="18">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>46021</v>
       </c>
       <c r="BN26" s="16">
         <v>5</v>
       </c>
       <c r="BP26" s="18">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>45824</v>
       </c>
       <c r="BQ26" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>45929</v>
       </c>
       <c r="BR26" s="16">
         <v>75</v>
       </c>
       <c r="BT26" s="18">
+        <f t="shared" si="33"/>
         <v>45930</v>
       </c>
       <c r="BU26" s="18">
+        <f t="shared" si="34"/>
         <v>46021</v>
       </c>
       <c r="BV26" s="16">
         <v>3</v>
       </c>
       <c r="BX26" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>46022</v>
       </c>
       <c r="BY26" s="18">
@@ -13614,33 +13690,33 @@
         <v>0</v>
       </c>
       <c r="CB26" s="22">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>45359</v>
       </c>
       <c r="CC26" s="22">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>45471</v>
       </c>
       <c r="CD26" s="16">
         <v>80</v>
       </c>
       <c r="CF26" s="22">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>45473</v>
       </c>
       <c r="CG26" s="22">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>46021</v>
       </c>
       <c r="CH26" s="16">
         <v>18</v>
       </c>
       <c r="CJ26" s="22">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>46022</v>
       </c>
       <c r="CK26" s="18">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>46022</v>
       </c>
       <c r="CL26" s="16">
@@ -13653,11 +13729,11 @@
         <v>45901</v>
       </c>
       <c r="CP26" s="77">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>45717</v>
       </c>
       <c r="CQ26" s="22">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>45778</v>
       </c>
       <c r="CR26" s="78">
@@ -13665,11 +13741,11 @@
       </c>
       <c r="CS26" s="73"/>
       <c r="CT26" s="77">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>45778</v>
       </c>
       <c r="CU26" s="22">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>45839</v>
       </c>
       <c r="CV26" s="78">
@@ -13677,11 +13753,11 @@
       </c>
       <c r="CW26" s="73"/>
       <c r="CX26" s="77">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>45839</v>
       </c>
       <c r="CY26" s="22">
-        <f t="shared" si="43"/>
+        <f t="shared" si="47"/>
         <v>45901</v>
       </c>
       <c r="CZ26" s="78">
@@ -13689,11 +13765,11 @@
       </c>
       <c r="DA26" s="73"/>
       <c r="DB26" s="77">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>45901</v>
       </c>
       <c r="DC26" s="22">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>45962</v>
       </c>
       <c r="DD26" s="78">
@@ -13701,11 +13777,11 @@
       </c>
       <c r="DE26" s="74"/>
       <c r="DF26" s="77">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>45962</v>
       </c>
       <c r="DG26" s="22">
-        <f t="shared" si="47"/>
+        <f t="shared" si="51"/>
         <v>46174</v>
       </c>
       <c r="DH26" s="78">
@@ -13738,7 +13814,7 @@
         <v>46020</v>
       </c>
       <c r="K27" s="31">
-        <f t="shared" si="48"/>
+        <f t="shared" si="52"/>
         <v>46567</v>
       </c>
       <c r="L27" s="29">
@@ -13749,7 +13825,7 @@
         <v>46568</v>
       </c>
       <c r="O27" s="31">
-        <f t="shared" si="49"/>
+        <f t="shared" si="53"/>
         <v>46568</v>
       </c>
       <c r="P27" s="33">
@@ -13872,47 +13948,51 @@
         <v>155</v>
       </c>
       <c r="BH27" s="31">
+        <f t="shared" si="27"/>
         <v>46259</v>
       </c>
       <c r="BI27" s="31">
+        <f t="shared" si="28"/>
         <v>46385</v>
       </c>
       <c r="BJ27" s="29">
         <v>90</v>
       </c>
       <c r="BL27" s="31">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>46386</v>
       </c>
       <c r="BM27" s="31">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>46537</v>
       </c>
       <c r="BN27" s="29">
         <v>5</v>
       </c>
       <c r="BP27" s="31">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>46339</v>
       </c>
       <c r="BQ27" s="31">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>46444</v>
       </c>
       <c r="BR27" s="29">
         <v>75</v>
       </c>
       <c r="BT27" s="31">
+        <f t="shared" si="33"/>
         <v>46446</v>
       </c>
       <c r="BU27" s="31">
+        <f t="shared" si="34"/>
         <v>46535</v>
       </c>
       <c r="BV27" s="29">
         <v>3</v>
       </c>
       <c r="BX27" s="31">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>46538</v>
       </c>
       <c r="BY27" s="31">
@@ -13923,33 +14003,33 @@
         <v>0</v>
       </c>
       <c r="CB27" s="34">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>45876</v>
       </c>
       <c r="CC27" s="34">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>45988</v>
       </c>
       <c r="CD27" s="29">
         <v>80</v>
       </c>
       <c r="CF27" s="34">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>45989</v>
       </c>
       <c r="CG27" s="34">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>46535</v>
       </c>
       <c r="CH27" s="29">
         <v>18</v>
       </c>
       <c r="CJ27" s="34">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>46538</v>
       </c>
       <c r="CK27" s="18">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>46538</v>
       </c>
       <c r="CL27" s="29">
@@ -13962,11 +14042,11 @@
         <v>46569</v>
       </c>
       <c r="CP27" s="79">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>46388</v>
       </c>
       <c r="CQ27" s="34">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>46447</v>
       </c>
       <c r="CR27" s="80">
@@ -13974,11 +14054,11 @@
       </c>
       <c r="CS27" s="73"/>
       <c r="CT27" s="79">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>46447</v>
       </c>
       <c r="CU27" s="34">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>46508</v>
       </c>
       <c r="CV27" s="80">
@@ -13986,11 +14066,11 @@
       </c>
       <c r="CW27" s="73"/>
       <c r="CX27" s="79">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>46508</v>
       </c>
       <c r="CY27" s="34">
-        <f t="shared" si="43"/>
+        <f t="shared" si="47"/>
         <v>46569</v>
       </c>
       <c r="CZ27" s="80">
@@ -13998,11 +14078,11 @@
       </c>
       <c r="DA27" s="73"/>
       <c r="DB27" s="79">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>46569</v>
       </c>
       <c r="DC27" s="34">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>46631</v>
       </c>
       <c r="DD27" s="80">
@@ -14010,11 +14090,11 @@
       </c>
       <c r="DE27" s="74"/>
       <c r="DF27" s="79">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>46631</v>
       </c>
       <c r="DG27" s="34">
-        <f t="shared" si="47"/>
+        <f t="shared" si="51"/>
         <v>46844</v>
       </c>
       <c r="DH27" s="80">
@@ -14047,7 +14127,7 @@
         <v>46598</v>
       </c>
       <c r="K28" s="18">
-        <f t="shared" si="48"/>
+        <f t="shared" si="52"/>
         <v>47148</v>
       </c>
       <c r="L28" s="16">
@@ -14058,7 +14138,7 @@
         <v>47149</v>
       </c>
       <c r="O28" s="18">
-        <f t="shared" si="49"/>
+        <f t="shared" si="53"/>
         <v>47149</v>
       </c>
       <c r="P28" s="20">
@@ -14181,47 +14261,51 @@
         <v>155</v>
       </c>
       <c r="BH28" s="18">
+        <f t="shared" si="27"/>
         <v>46836</v>
       </c>
       <c r="BI28" s="18">
+        <f t="shared" si="28"/>
         <v>46962</v>
       </c>
       <c r="BJ28" s="16">
         <v>90</v>
       </c>
       <c r="BL28" s="18">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>46965</v>
       </c>
       <c r="BM28" s="18">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>47118</v>
       </c>
       <c r="BN28" s="16">
         <v>5</v>
       </c>
       <c r="BP28" s="18">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>46919</v>
       </c>
       <c r="BQ28" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>47024</v>
       </c>
       <c r="BR28" s="16">
         <v>75</v>
       </c>
       <c r="BT28" s="18">
+        <f t="shared" si="33"/>
         <v>47025</v>
       </c>
       <c r="BU28" s="18">
+        <f t="shared" si="34"/>
         <v>47116</v>
       </c>
       <c r="BV28" s="16">
         <v>3</v>
       </c>
       <c r="BX28" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>47119</v>
       </c>
       <c r="BY28" s="18">
@@ -14232,33 +14316,33 @@
         <v>0</v>
       </c>
       <c r="CB28" s="22">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>46454</v>
       </c>
       <c r="CC28" s="22">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>46566</v>
       </c>
       <c r="CD28" s="16">
         <v>80</v>
       </c>
       <c r="CF28" s="22">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>46567</v>
       </c>
       <c r="CG28" s="22">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>47116</v>
       </c>
       <c r="CH28" s="16">
         <v>18</v>
       </c>
       <c r="CJ28" s="22">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>47119</v>
       </c>
       <c r="CK28" s="18">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>47119</v>
       </c>
       <c r="CL28" s="16">
@@ -14271,11 +14355,11 @@
         <v>47150</v>
       </c>
       <c r="CP28" s="77">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>46966</v>
       </c>
       <c r="CQ28" s="22">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>47027</v>
       </c>
       <c r="CR28" s="78">
@@ -14283,11 +14367,11 @@
       </c>
       <c r="CS28" s="73"/>
       <c r="CT28" s="77">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>47027</v>
       </c>
       <c r="CU28" s="22">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>47088</v>
       </c>
       <c r="CV28" s="78">
@@ -14295,11 +14379,11 @@
       </c>
       <c r="CW28" s="73"/>
       <c r="CX28" s="77">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>47088</v>
       </c>
       <c r="CY28" s="22">
-        <f t="shared" si="43"/>
+        <f t="shared" si="47"/>
         <v>47150</v>
       </c>
       <c r="CZ28" s="78">
@@ -14307,11 +14391,11 @@
       </c>
       <c r="DA28" s="73"/>
       <c r="DB28" s="77">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>47150</v>
       </c>
       <c r="DC28" s="22">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>47209</v>
       </c>
       <c r="DD28" s="78">
@@ -14319,11 +14403,11 @@
       </c>
       <c r="DE28" s="74"/>
       <c r="DF28" s="77">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>47209</v>
       </c>
       <c r="DG28" s="22">
-        <f t="shared" si="47"/>
+        <f t="shared" si="51"/>
         <v>47423</v>
       </c>
       <c r="DH28" s="78">
@@ -14356,7 +14440,7 @@
         <v>47148</v>
       </c>
       <c r="K29" s="31">
-        <f t="shared" si="48"/>
+        <f t="shared" si="52"/>
         <v>47694</v>
       </c>
       <c r="L29" s="29">
@@ -14367,7 +14451,7 @@
         <v>47695</v>
       </c>
       <c r="O29" s="31">
-        <f t="shared" si="49"/>
+        <f t="shared" si="53"/>
         <v>47695</v>
       </c>
       <c r="P29" s="33">
@@ -14490,47 +14574,51 @@
         <v>155</v>
       </c>
       <c r="BH29" s="31">
+        <f t="shared" si="27"/>
         <v>47401</v>
       </c>
       <c r="BI29" s="31">
+        <f t="shared" si="28"/>
         <v>47527</v>
       </c>
       <c r="BJ29" s="29">
         <v>90</v>
       </c>
       <c r="BL29" s="31">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>47528</v>
       </c>
       <c r="BM29" s="31">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>47678</v>
       </c>
       <c r="BN29" s="29">
         <v>5</v>
       </c>
       <c r="BP29" s="31">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>47479</v>
       </c>
       <c r="BQ29" s="31">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>47584</v>
       </c>
       <c r="BR29" s="29">
         <v>75</v>
       </c>
       <c r="BT29" s="31">
+        <f t="shared" si="33"/>
         <v>47585</v>
       </c>
       <c r="BU29" s="31">
+        <f t="shared" si="34"/>
         <v>47676</v>
       </c>
       <c r="BV29" s="29">
         <v>3</v>
       </c>
       <c r="BX29" s="31">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>47679</v>
       </c>
       <c r="BY29" s="31">
@@ -14541,33 +14629,33 @@
         <v>0</v>
       </c>
       <c r="CB29" s="34">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>47017</v>
       </c>
       <c r="CC29" s="34">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>47129</v>
       </c>
       <c r="CD29" s="29">
         <v>80</v>
       </c>
       <c r="CF29" s="34">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>47130</v>
       </c>
       <c r="CG29" s="34">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>47676</v>
       </c>
       <c r="CH29" s="29">
         <v>18</v>
       </c>
       <c r="CJ29" s="34">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>47679</v>
       </c>
       <c r="CK29" s="18">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>47679</v>
       </c>
       <c r="CL29" s="29">
@@ -14580,11 +14668,11 @@
         <v>47696</v>
       </c>
       <c r="CP29" s="79">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>47515</v>
       </c>
       <c r="CQ29" s="34">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>47574</v>
       </c>
       <c r="CR29" s="80">
@@ -14592,11 +14680,11 @@
       </c>
       <c r="CS29" s="73"/>
       <c r="CT29" s="79">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>47574</v>
       </c>
       <c r="CU29" s="34">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>47635</v>
       </c>
       <c r="CV29" s="80">
@@ -14604,11 +14692,11 @@
       </c>
       <c r="CW29" s="73"/>
       <c r="CX29" s="79">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>47635</v>
       </c>
       <c r="CY29" s="34">
-        <f t="shared" si="43"/>
+        <f t="shared" si="47"/>
         <v>47696</v>
       </c>
       <c r="CZ29" s="80">
@@ -14616,11 +14704,11 @@
       </c>
       <c r="DA29" s="73"/>
       <c r="DB29" s="79">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>47696</v>
       </c>
       <c r="DC29" s="34">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>47757</v>
       </c>
       <c r="DD29" s="80">
@@ -14628,11 +14716,11 @@
       </c>
       <c r="DE29" s="74"/>
       <c r="DF29" s="79">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>47757</v>
       </c>
       <c r="DG29" s="34">
-        <f t="shared" si="47"/>
+        <f t="shared" si="51"/>
         <v>47969</v>
       </c>
       <c r="DH29" s="80">
@@ -14666,7 +14754,7 @@
         <v>45838</v>
       </c>
       <c r="K30" s="41">
-        <f t="shared" si="48"/>
+        <f t="shared" si="52"/>
         <v>46386</v>
       </c>
       <c r="L30" s="42">
@@ -14678,7 +14766,7 @@
         <v>46387</v>
       </c>
       <c r="O30" s="41">
-        <f t="shared" si="49"/>
+        <f t="shared" si="53"/>
         <v>46387</v>
       </c>
       <c r="P30" s="44">
@@ -14801,47 +14889,51 @@
         <v>155</v>
       </c>
       <c r="BH30" s="47">
+        <f t="shared" si="27"/>
         <v>46106</v>
       </c>
       <c r="BI30" s="47">
+        <f t="shared" si="28"/>
         <v>46232</v>
       </c>
       <c r="BJ30" s="39">
         <v>90</v>
       </c>
       <c r="BL30" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>46233</v>
       </c>
       <c r="BM30" s="47">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>46386</v>
       </c>
       <c r="BN30" s="39">
         <v>5</v>
       </c>
       <c r="BP30" s="47">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>46189</v>
       </c>
       <c r="BQ30" s="47">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>46294</v>
       </c>
       <c r="BR30" s="39">
         <v>75</v>
       </c>
       <c r="BT30" s="47">
+        <f t="shared" si="33"/>
         <v>46295</v>
       </c>
       <c r="BU30" s="47">
+        <f t="shared" si="34"/>
         <v>46386</v>
       </c>
       <c r="BV30" s="39">
         <v>3</v>
       </c>
       <c r="BX30" s="47">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>46387</v>
       </c>
       <c r="BY30" s="47">
@@ -14852,33 +14944,33 @@
         <v>0</v>
       </c>
       <c r="CB30" s="46">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>45723</v>
       </c>
       <c r="CC30" s="46">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>45835</v>
       </c>
       <c r="CD30" s="39">
         <v>80</v>
       </c>
       <c r="CF30" s="46">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>45838</v>
       </c>
       <c r="CG30" s="46">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>46386</v>
       </c>
       <c r="CH30" s="39">
         <v>18</v>
       </c>
       <c r="CJ30" s="46">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>46387</v>
       </c>
       <c r="CK30" s="18">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>46387</v>
       </c>
       <c r="CL30" s="39">
@@ -14891,11 +14983,11 @@
         <v>46388</v>
       </c>
       <c r="CP30" s="81">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>46204</v>
       </c>
       <c r="CQ30" s="82">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>46266</v>
       </c>
       <c r="CR30" s="83">
@@ -14903,11 +14995,11 @@
       </c>
       <c r="CS30" s="84"/>
       <c r="CT30" s="81">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>46266</v>
       </c>
       <c r="CU30" s="82">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>46327</v>
       </c>
       <c r="CV30" s="83">
@@ -14915,11 +15007,11 @@
       </c>
       <c r="CW30" s="84"/>
       <c r="CX30" s="81">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>46327</v>
       </c>
       <c r="CY30" s="82">
-        <f t="shared" si="43"/>
+        <f t="shared" si="47"/>
         <v>46388</v>
       </c>
       <c r="CZ30" s="83">
@@ -14927,11 +15019,11 @@
       </c>
       <c r="DA30" s="84"/>
       <c r="DB30" s="81">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>46388</v>
       </c>
       <c r="DC30" s="82">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>46447</v>
       </c>
       <c r="DD30" s="83">
@@ -14939,11 +15031,11 @@
       </c>
       <c r="DE30" s="85"/>
       <c r="DF30" s="81">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>46447</v>
       </c>
       <c r="DG30" s="82">
-        <f t="shared" si="47"/>
+        <f t="shared" si="51"/>
         <v>46661</v>
       </c>
       <c r="DH30" s="83">
@@ -14952,14 +15044,17 @@
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="BH3:BJ3"/>
-    <mergeCell ref="CJ3:CL3"/>
-    <mergeCell ref="BL3:BN3"/>
-    <mergeCell ref="BP3:BR3"/>
-    <mergeCell ref="BT3:BV3"/>
-    <mergeCell ref="BX3:BZ3"/>
-    <mergeCell ref="CB3:CD3"/>
-    <mergeCell ref="CF3:CH3"/>
+    <mergeCell ref="CP2:DH2"/>
+    <mergeCell ref="CP3:CR3"/>
+    <mergeCell ref="CT3:CV3"/>
+    <mergeCell ref="CX3:CZ3"/>
+    <mergeCell ref="DB3:DD3"/>
+    <mergeCell ref="DF3:DH3"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="F2:Q2"/>
+    <mergeCell ref="S2:AG2"/>
+    <mergeCell ref="AI2:AX2"/>
+    <mergeCell ref="AZ2:BN2"/>
     <mergeCell ref="BX2:BZ2"/>
     <mergeCell ref="CF2:CN2"/>
     <mergeCell ref="F3:H3"/>
@@ -14976,17 +15071,14 @@
     <mergeCell ref="AV3:AX3"/>
     <mergeCell ref="AZ3:BB3"/>
     <mergeCell ref="BD3:BF3"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="F2:Q2"/>
-    <mergeCell ref="S2:AG2"/>
-    <mergeCell ref="AI2:AX2"/>
-    <mergeCell ref="AZ2:BN2"/>
-    <mergeCell ref="CP2:DH2"/>
-    <mergeCell ref="CP3:CR3"/>
-    <mergeCell ref="CT3:CV3"/>
-    <mergeCell ref="CX3:CZ3"/>
-    <mergeCell ref="DB3:DD3"/>
-    <mergeCell ref="DF3:DH3"/>
+    <mergeCell ref="BH3:BJ3"/>
+    <mergeCell ref="CJ3:CL3"/>
+    <mergeCell ref="BL3:BN3"/>
+    <mergeCell ref="BP3:BR3"/>
+    <mergeCell ref="BT3:BV3"/>
+    <mergeCell ref="BX3:BZ3"/>
+    <mergeCell ref="CB3:CD3"/>
+    <mergeCell ref="CF3:CH3"/>
   </mergeCells>
   <conditionalFormatting sqref="J8:J30">
     <cfRule type="cellIs" dxfId="13" priority="25" operator="lessThan">
@@ -15079,12 +15171,12 @@
   <sheetData>
     <row r="1" spans="2:24" ht="8.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:24" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="B2" s="105" t="s">
+      <c r="B2" s="109" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
-      <c r="E2" s="105"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="109"/>
+      <c r="E2" s="109"/>
     </row>
     <row r="3" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B3" s="54" t="s">
